--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -221,16 +221,16 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
+    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>NC</t>
@@ -1067,7 +1067,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -1121,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>-1</v>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -1207,7 +1207,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1221,7 +1221,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>-1</v>
@@ -1230,13 +1230,13 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>-1</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1275,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1284,13 +1284,13 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>-1</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1298,7 +1298,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -1307,13 +1307,13 @@
         <v>10</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1352,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1361,13 +1361,13 @@
         <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1384,13 +1384,13 @@
         <v>10</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>-1</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1438,13 +1438,13 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1452,7 +1452,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1506,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1515,7 +1515,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>-1</v>
@@ -1529,7 +1529,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1538,13 +1538,13 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>-1</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1583,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1592,13 +1592,13 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1606,7 +1606,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>-1</v>
@@ -1615,13 +1615,13 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>-1</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1660,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1669,13 +1669,13 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>-1</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1683,7 +1683,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>-1</v>
@@ -1692,13 +1692,13 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F12">
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1746,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1760,7 +1760,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>-1</v>
@@ -1769,13 +1769,13 @@
         <v>10</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>-1</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1823,13 +1823,13 @@
         <v>10</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1846,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -1900,7 +1900,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1923,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>-1</v>
@@ -1977,7 +1977,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>-1</v>
@@ -2000,13 +2000,13 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F16">
         <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -2054,13 +2054,13 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2068,7 +2068,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -2077,13 +2077,13 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2131,13 +2131,13 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2145,7 +2145,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2154,7 +2154,7 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -2222,7 +2222,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2231,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2285,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2299,7 +2299,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>-1</v>
@@ -2308,13 +2308,13 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2362,13 +2362,13 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2376,7 +2376,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2385,13 +2385,13 @@
         <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2439,13 +2439,13 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>-1</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2516,7 +2516,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2530,7 +2530,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -2539,7 +2539,7 @@
         <v>9</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2593,7 +2593,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2607,7 +2607,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>-1</v>
@@ -2616,7 +2616,7 @@
         <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2661,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2670,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2684,7 +2684,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C25">
         <v>-1</v>
@@ -2693,13 +2693,13 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>-1</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2738,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>-1</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2761,7 +2761,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -2770,13 +2770,13 @@
         <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>-1</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2815,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2824,13 +2824,13 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2838,7 +2838,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C27">
         <v>-1</v>
@@ -2847,13 +2847,13 @@
         <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>-1</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2901,13 +2901,13 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>-1</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2915,7 +2915,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>-1</v>
@@ -2924,13 +2924,13 @@
         <v>10</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2969,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2978,13 +2978,13 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3001,13 +3001,13 @@
         <v>10</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>-1</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -3055,13 +3055,13 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3069,7 +3069,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>-1</v>
@@ -3078,13 +3078,13 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
         <v>-1</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3132,13 +3132,13 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>-1</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3146,7 +3146,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>-1</v>
@@ -3155,7 +3155,7 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>-1</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3209,7 +3209,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>-1</v>
@@ -3223,7 +3223,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>-1</v>
@@ -3232,13 +3232,13 @@
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3286,13 +3286,13 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3300,7 +3300,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3309,13 +3309,13 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3363,13 +3363,13 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>-1</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3377,7 +3377,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C34">
         <v>-1</v>
@@ -3386,13 +3386,13 @@
         <v>10</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3431,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3440,13 +3440,13 @@
         <v>10</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>-1</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3454,7 +3454,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3463,13 +3463,13 @@
         <v>10</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3508,7 +3508,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3517,13 +3517,13 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>-1</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3540,13 +3540,13 @@
         <v>9</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3594,13 +3594,13 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>-1</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3608,7 +3608,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -3617,13 +3617,13 @@
         <v>10</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3662,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3671,13 +3671,13 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>-1</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3685,7 +3685,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C38">
         <v>-1</v>
@@ -3694,13 +3694,13 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F38">
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3739,7 +3739,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3748,13 +3748,13 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>-1</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3762,7 +3762,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>-1</v>
@@ -3771,13 +3771,13 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3816,7 +3816,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3825,13 +3825,13 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3839,7 +3839,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>-1</v>
@@ -3848,13 +3848,13 @@
         <v>9</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -3902,13 +3902,13 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>-1</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3925,7 +3925,7 @@
         <v>8</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>-1</v>
@@ -3979,7 +3979,7 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>-1</v>
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F42">
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>-1</v>
@@ -4056,13 +4056,13 @@
         <v>8</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X42">
         <v>-1</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4070,7 +4070,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C43">
         <v>-1</v>
@@ -4079,13 +4079,13 @@
         <v>9</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -4124,7 +4124,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -4133,13 +4133,13 @@
         <v>9</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>-1</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4147,7 +4147,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C44">
         <v>-1</v>
@@ -4156,13 +4156,13 @@
         <v>9</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H44">
         <v>-1</v>
@@ -4201,7 +4201,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U44">
         <v>-1</v>
@@ -4210,13 +4210,13 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>-1</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4224,7 +4224,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C45">
         <v>-1</v>
@@ -4233,13 +4233,13 @@
         <v>8</v>
       </c>
       <c r="E45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F45">
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H45">
         <v>-1</v>
@@ -4278,7 +4278,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>-1</v>
@@ -4287,13 +4287,13 @@
         <v>8</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X45">
         <v>-1</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4310,13 +4310,13 @@
         <v>10</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H46">
         <v>-1</v>
@@ -4364,13 +4364,13 @@
         <v>10</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X46">
         <v>-1</v>
       </c>
       <c r="Y46">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4378,7 +4378,7 @@
         <v>55</v>
       </c>
       <c r="B47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C47">
         <v>-1</v>
@@ -4387,13 +4387,13 @@
         <v>9</v>
       </c>
       <c r="E47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H47">
         <v>-1</v>
@@ -4432,7 +4432,7 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U47">
         <v>-1</v>
@@ -4441,13 +4441,13 @@
         <v>9</v>
       </c>
       <c r="W47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X47">
         <v>-1</v>
       </c>
       <c r="Y47">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4570,27 +4570,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>7.7</v>
+      </c>
       <c r="I4">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4599,27 +4602,30 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I5">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4628,27 +4634,30 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>9.300000000000001</v>
+      </c>
       <c r="I6">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -4669,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4685,7 +4694,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4766,7 +4775,7 @@
         <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -4774,42 +4783,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4826,10 +4835,10 @@
         <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4846,284 +4855,284 @@
         <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920252</v>
+        <v>21330051920253</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920252</v>
+        <v>21330051920253</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920252</v>
+        <v>21330051920254</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920253</v>
+        <v>21330051920254</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920253</v>
+        <v>21330051920255</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920253</v>
+        <v>21330051920255</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920253</v>
+        <v>21330051920255</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920253</v>
+        <v>21330051920256</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920254</v>
+        <v>21330051920256</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920254</v>
+        <v>21330051920257</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920254</v>
+        <v>21330051920257</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920254</v>
+        <v>21330051920258</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920254</v>
+        <v>21330051920258</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920255</v>
+        <v>21330051920259</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -5134,16 +5143,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920255</v>
+        <v>21330051920259</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -5154,139 +5163,139 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920255</v>
+        <v>21330051920260</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920255</v>
+        <v>21330051920260</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920255</v>
+        <v>21330051920260</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920256</v>
+        <v>21330051920260</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920256</v>
+        <v>21330051920261</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920256</v>
+        <v>21330051920261</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920256</v>
+        <v>21330051920261</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
         <v>68</v>
@@ -5294,36 +5303,36 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920256</v>
+        <v>21330051920261</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920257</v>
+        <v>21330051920262</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -5334,16 +5343,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920257</v>
+        <v>21330051920262</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -5354,76 +5363,76 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920257</v>
+        <v>21330051920262</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920257</v>
+        <v>21330051920263</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920257</v>
+        <v>21330051920263</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920258</v>
+        <v>21330051920264</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -5434,16 +5443,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920258</v>
+        <v>21330051920264</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
@@ -5454,76 +5463,76 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920258</v>
+        <v>21330051920265</v>
       </c>
       <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
         <v>82</v>
       </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920258</v>
+        <v>21330051920265</v>
       </c>
       <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
         <v>82</v>
       </c>
-      <c r="C40" t="s">
-        <v>121</v>
-      </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920258</v>
+        <v>21330051920265</v>
       </c>
       <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
         <v>82</v>
       </c>
-      <c r="C41" t="s">
-        <v>121</v>
-      </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920259</v>
+        <v>21330051920266</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -5534,16 +5543,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920259</v>
+        <v>21330051920266</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
         <v>6</v>
@@ -5554,76 +5563,76 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920259</v>
+        <v>21330051920267</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D44" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920259</v>
+        <v>21330051920267</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920259</v>
+        <v>21330051920267</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D46" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920260</v>
+        <v>21330051920087</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D47" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -5634,16 +5643,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920260</v>
+        <v>21330051920087</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
@@ -5654,376 +5663,376 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920260</v>
+        <v>21330051920088</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920260</v>
+        <v>21330051920088</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920260</v>
+        <v>21330051920088</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920261</v>
+        <v>21330051920088</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920261</v>
+        <v>21330051920358</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920261</v>
+        <v>21330051920358</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920261</v>
+        <v>21330051920358</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920261</v>
+        <v>21330051920268</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920262</v>
+        <v>21330051920268</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D57" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920262</v>
+        <v>21330051920268</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920262</v>
+        <v>21330051920091</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E59" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920262</v>
+        <v>21330051920091</v>
       </c>
       <c r="B60" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920262</v>
+        <v>21330051920270</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920263</v>
+        <v>21330051920270</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F62" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920263</v>
+        <v>21330051920271</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920263</v>
+        <v>21330051920271</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="E64" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920263</v>
+        <v>21330051920272</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D65" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920263</v>
+        <v>21330051920272</v>
       </c>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920264</v>
+        <v>21330051920273</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -6034,16 +6043,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920264</v>
+        <v>21330051920273</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
@@ -6054,76 +6063,76 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920264</v>
+        <v>21330051920273</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E69" t="s">
         <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920264</v>
+        <v>21330051920274</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920264</v>
+        <v>21330051920274</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="E71" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920265</v>
+        <v>21330051920361</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -6134,16 +6143,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920265</v>
+        <v>21330051920361</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C73" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E73" t="s">
         <v>6</v>
@@ -6154,19 +6163,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920265</v>
+        <v>21330051920361</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E74" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F74" t="s">
         <v>67</v>
@@ -6174,56 +6183,56 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920265</v>
+        <v>21330051920275</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920265</v>
+        <v>21330051920275</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E76" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F76" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920266</v>
+        <v>21330051920362</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D77" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -6234,16 +6243,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>21330051920266</v>
+        <v>21330051920362</v>
       </c>
       <c r="B78" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E78" t="s">
         <v>6</v>
@@ -6254,276 +6263,276 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>21330051920266</v>
+        <v>21330051920276</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D79" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>21330051920266</v>
+        <v>21330051920276</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D80" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F80" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>21330051920266</v>
+        <v>21330051920277</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>21330051920267</v>
+        <v>21330051920277</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D82" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E82" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F82" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>21330051920267</v>
+        <v>21330051920278</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E83" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>21330051920267</v>
+        <v>21330051920278</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D84" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>21330051920267</v>
+        <v>21330051420149</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C85" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>21330051920267</v>
+        <v>21330051420149</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F86" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>21330051920087</v>
+        <v>21330051420149</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D87" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E87" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F87" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>21330051920087</v>
+        <v>21330051920279</v>
       </c>
       <c r="B88" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C88" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D88" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="E88" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>21330051920087</v>
+        <v>21330051920279</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C89" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D89" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="E89" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>21330051920087</v>
+        <v>21330051920280</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C90" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="D90" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91">
-        <v>21330051920087</v>
+        <v>21330051920280</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C91" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F91" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>21330051920088</v>
+        <v>21330051920282</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C92" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D92" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
@@ -6534,16 +6543,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>21330051920088</v>
+        <v>21330051920282</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D93" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E93" t="s">
         <v>6</v>
@@ -6554,276 +6563,276 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>21330051920088</v>
+        <v>21330051920282</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E94" t="s">
         <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>21330051920088</v>
+        <v>21330051920282</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D95" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>21330051920088</v>
+        <v>21330051920283</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>21330051920358</v>
+        <v>21330051920283</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E97" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F97" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>21330051920358</v>
+        <v>21330051920284</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D98" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E98" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>21330051920358</v>
+        <v>21330051920284</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C99" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D99" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E99" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F99" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>21330051920358</v>
+        <v>21330051920285</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D100" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>21330051920358</v>
+        <v>21330051920285</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D101" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E101" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F101" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>21330051920268</v>
+        <v>21330051920285</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C102" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="D102" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F102" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>21330051920268</v>
+        <v>21330051920286</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C103" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="D103" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E103" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F103" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104">
-        <v>21330051920268</v>
+        <v>21330051920286</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="D104" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E104" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F104" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105">
-        <v>21330051920268</v>
+        <v>20330051920358</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C105" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D105" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106">
-        <v>21330051920268</v>
+        <v>20330051920358</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C106" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D106" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F106" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107">
-        <v>21330051920091</v>
+        <v>21330051920287</v>
       </c>
       <c r="B107" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="D107" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
@@ -6834,16 +6843,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108">
-        <v>21330051920091</v>
+        <v>21330051920287</v>
       </c>
       <c r="B108" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="D108" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E108" t="s">
         <v>6</v>
@@ -6854,2262 +6863,62 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109">
-        <v>21330051920091</v>
+        <v>21330051920288</v>
       </c>
       <c r="B109" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D109" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E109" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F109" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110">
-        <v>21330051920091</v>
+        <v>21330051920288</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D110" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E110" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F110" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111">
-        <v>21330051920091</v>
+        <v>21330051920288</v>
       </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F111" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920270</v>
-      </c>
-      <c r="B112" t="s">
-        <v>95</v>
-      </c>
-      <c r="C112" t="s">
-        <v>131</v>
-      </c>
-      <c r="D112" t="s">
-        <v>166</v>
-      </c>
-      <c r="E112" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920270</v>
-      </c>
-      <c r="B113" t="s">
-        <v>95</v>
-      </c>
-      <c r="C113" t="s">
-        <v>131</v>
-      </c>
-      <c r="D113" t="s">
-        <v>166</v>
-      </c>
-      <c r="E113" t="s">
-        <v>6</v>
-      </c>
-      <c r="F113" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920270</v>
-      </c>
-      <c r="B114" t="s">
-        <v>95</v>
-      </c>
-      <c r="C114" t="s">
-        <v>131</v>
-      </c>
-      <c r="D114" t="s">
-        <v>166</v>
-      </c>
-      <c r="E114" t="s">
-        <v>5</v>
-      </c>
-      <c r="F114" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920270</v>
-      </c>
-      <c r="B115" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" t="s">
-        <v>131</v>
-      </c>
-      <c r="D115" t="s">
-        <v>166</v>
-      </c>
-      <c r="E115" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920270</v>
-      </c>
-      <c r="B116" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" t="s">
-        <v>131</v>
-      </c>
-      <c r="D116" t="s">
-        <v>166</v>
-      </c>
-      <c r="E116" t="s">
-        <v>8</v>
-      </c>
-      <c r="F116" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920271</v>
-      </c>
-      <c r="B117" t="s">
-        <v>96</v>
-      </c>
-      <c r="C117" t="s">
-        <v>132</v>
-      </c>
-      <c r="D117" t="s">
-        <v>167</v>
-      </c>
-      <c r="E117" t="s">
-        <v>9</v>
-      </c>
-      <c r="F117" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920271</v>
-      </c>
-      <c r="B118" t="s">
-        <v>96</v>
-      </c>
-      <c r="C118" t="s">
-        <v>132</v>
-      </c>
-      <c r="D118" t="s">
-        <v>167</v>
-      </c>
-      <c r="E118" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920271</v>
-      </c>
-      <c r="B119" t="s">
-        <v>96</v>
-      </c>
-      <c r="C119" t="s">
-        <v>132</v>
-      </c>
-      <c r="D119" t="s">
-        <v>167</v>
-      </c>
-      <c r="E119" t="s">
-        <v>5</v>
-      </c>
-      <c r="F119" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>21330051920271</v>
-      </c>
-      <c r="B120" t="s">
-        <v>96</v>
-      </c>
-      <c r="C120" t="s">
-        <v>132</v>
-      </c>
-      <c r="D120" t="s">
-        <v>167</v>
-      </c>
-      <c r="E120" t="s">
-        <v>10</v>
-      </c>
-      <c r="F120" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>21330051920271</v>
-      </c>
-      <c r="B121" t="s">
-        <v>96</v>
-      </c>
-      <c r="C121" t="s">
-        <v>132</v>
-      </c>
-      <c r="D121" t="s">
-        <v>167</v>
-      </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>21330051920272</v>
-      </c>
-      <c r="B122" t="s">
-        <v>97</v>
-      </c>
-      <c r="C122" t="s">
-        <v>133</v>
-      </c>
-      <c r="D122" t="s">
-        <v>168</v>
-      </c>
-      <c r="E122" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>21330051920272</v>
-      </c>
-      <c r="B123" t="s">
-        <v>97</v>
-      </c>
-      <c r="C123" t="s">
-        <v>133</v>
-      </c>
-      <c r="D123" t="s">
-        <v>168</v>
-      </c>
-      <c r="E123" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>21330051920272</v>
-      </c>
-      <c r="B124" t="s">
-        <v>97</v>
-      </c>
-      <c r="C124" t="s">
-        <v>133</v>
-      </c>
-      <c r="D124" t="s">
-        <v>168</v>
-      </c>
-      <c r="E124" t="s">
-        <v>5</v>
-      </c>
-      <c r="F124" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>21330051920272</v>
-      </c>
-      <c r="B125" t="s">
-        <v>97</v>
-      </c>
-      <c r="C125" t="s">
-        <v>133</v>
-      </c>
-      <c r="D125" t="s">
-        <v>168</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>21330051920272</v>
-      </c>
-      <c r="B126" t="s">
-        <v>97</v>
-      </c>
-      <c r="C126" t="s">
-        <v>133</v>
-      </c>
-      <c r="D126" t="s">
-        <v>168</v>
-      </c>
-      <c r="E126" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>21330051920273</v>
-      </c>
-      <c r="B127" t="s">
-        <v>98</v>
-      </c>
-      <c r="C127" t="s">
-        <v>134</v>
-      </c>
-      <c r="D127" t="s">
-        <v>169</v>
-      </c>
-      <c r="E127" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>21330051920273</v>
-      </c>
-      <c r="B128" t="s">
-        <v>98</v>
-      </c>
-      <c r="C128" t="s">
-        <v>134</v>
-      </c>
-      <c r="D128" t="s">
-        <v>169</v>
-      </c>
-      <c r="E128" t="s">
-        <v>6</v>
-      </c>
-      <c r="F128" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>21330051920273</v>
-      </c>
-      <c r="B129" t="s">
-        <v>98</v>
-      </c>
-      <c r="C129" t="s">
-        <v>134</v>
-      </c>
-      <c r="D129" t="s">
-        <v>169</v>
-      </c>
-      <c r="E129" t="s">
-        <v>5</v>
-      </c>
-      <c r="F129" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>21330051920273</v>
-      </c>
-      <c r="B130" t="s">
-        <v>98</v>
-      </c>
-      <c r="C130" t="s">
-        <v>134</v>
-      </c>
-      <c r="D130" t="s">
-        <v>169</v>
-      </c>
-      <c r="E130" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>21330051920273</v>
-      </c>
-      <c r="B131" t="s">
-        <v>98</v>
-      </c>
-      <c r="C131" t="s">
-        <v>134</v>
-      </c>
-      <c r="D131" t="s">
-        <v>169</v>
-      </c>
-      <c r="E131" t="s">
-        <v>8</v>
-      </c>
-      <c r="F131" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>21330051920274</v>
-      </c>
-      <c r="B132" t="s">
-        <v>99</v>
-      </c>
-      <c r="C132" t="s">
-        <v>84</v>
-      </c>
-      <c r="D132" t="s">
-        <v>170</v>
-      </c>
-      <c r="E132" t="s">
-        <v>9</v>
-      </c>
-      <c r="F132" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>21330051920274</v>
-      </c>
-      <c r="B133" t="s">
-        <v>99</v>
-      </c>
-      <c r="C133" t="s">
-        <v>84</v>
-      </c>
-      <c r="D133" t="s">
-        <v>170</v>
-      </c>
-      <c r="E133" t="s">
-        <v>6</v>
-      </c>
-      <c r="F133" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>21330051920274</v>
-      </c>
-      <c r="B134" t="s">
-        <v>99</v>
-      </c>
-      <c r="C134" t="s">
-        <v>84</v>
-      </c>
-      <c r="D134" t="s">
-        <v>170</v>
-      </c>
-      <c r="E134" t="s">
-        <v>5</v>
-      </c>
-      <c r="F134" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>21330051920274</v>
-      </c>
-      <c r="B135" t="s">
-        <v>99</v>
-      </c>
-      <c r="C135" t="s">
-        <v>84</v>
-      </c>
-      <c r="D135" t="s">
-        <v>170</v>
-      </c>
-      <c r="E135" t="s">
-        <v>10</v>
-      </c>
-      <c r="F135" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>21330051920274</v>
-      </c>
-      <c r="B136" t="s">
-        <v>99</v>
-      </c>
-      <c r="C136" t="s">
-        <v>84</v>
-      </c>
-      <c r="D136" t="s">
-        <v>170</v>
-      </c>
-      <c r="E136" t="s">
-        <v>8</v>
-      </c>
-      <c r="F136" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>21330051920361</v>
-      </c>
-      <c r="B137" t="s">
-        <v>99</v>
-      </c>
-      <c r="C137" t="s">
-        <v>107</v>
-      </c>
-      <c r="D137" t="s">
-        <v>171</v>
-      </c>
-      <c r="E137" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>21330051920361</v>
-      </c>
-      <c r="B138" t="s">
-        <v>99</v>
-      </c>
-      <c r="C138" t="s">
-        <v>107</v>
-      </c>
-      <c r="D138" t="s">
-        <v>171</v>
-      </c>
-      <c r="E138" t="s">
-        <v>6</v>
-      </c>
-      <c r="F138" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>21330051920361</v>
-      </c>
-      <c r="B139" t="s">
-        <v>99</v>
-      </c>
-      <c r="C139" t="s">
-        <v>107</v>
-      </c>
-      <c r="D139" t="s">
-        <v>171</v>
-      </c>
-      <c r="E139" t="s">
-        <v>5</v>
-      </c>
-      <c r="F139" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>21330051920361</v>
-      </c>
-      <c r="B140" t="s">
-        <v>99</v>
-      </c>
-      <c r="C140" t="s">
-        <v>107</v>
-      </c>
-      <c r="D140" t="s">
-        <v>171</v>
-      </c>
-      <c r="E140" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>21330051920361</v>
-      </c>
-      <c r="B141" t="s">
-        <v>99</v>
-      </c>
-      <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="D141" t="s">
-        <v>171</v>
-      </c>
-      <c r="E141" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>21330051920275</v>
-      </c>
-      <c r="B142" t="s">
-        <v>100</v>
-      </c>
-      <c r="C142" t="s">
-        <v>107</v>
-      </c>
-      <c r="D142" t="s">
-        <v>172</v>
-      </c>
-      <c r="E142" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>21330051920275</v>
-      </c>
-      <c r="B143" t="s">
-        <v>100</v>
-      </c>
-      <c r="C143" t="s">
-        <v>107</v>
-      </c>
-      <c r="D143" t="s">
-        <v>172</v>
-      </c>
-      <c r="E143" t="s">
-        <v>6</v>
-      </c>
-      <c r="F143" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>21330051920275</v>
-      </c>
-      <c r="B144" t="s">
-        <v>100</v>
-      </c>
-      <c r="C144" t="s">
-        <v>107</v>
-      </c>
-      <c r="D144" t="s">
-        <v>172</v>
-      </c>
-      <c r="E144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>21330051920275</v>
-      </c>
-      <c r="B145" t="s">
-        <v>100</v>
-      </c>
-      <c r="C145" t="s">
-        <v>107</v>
-      </c>
-      <c r="D145" t="s">
-        <v>172</v>
-      </c>
-      <c r="E145" t="s">
-        <v>10</v>
-      </c>
-      <c r="F145" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>21330051920275</v>
-      </c>
-      <c r="B146" t="s">
-        <v>100</v>
-      </c>
-      <c r="C146" t="s">
-        <v>107</v>
-      </c>
-      <c r="D146" t="s">
-        <v>172</v>
-      </c>
-      <c r="E146" t="s">
-        <v>8</v>
-      </c>
-      <c r="F146" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>21330051920362</v>
-      </c>
-      <c r="B147" t="s">
-        <v>101</v>
-      </c>
-      <c r="C147" t="s">
-        <v>135</v>
-      </c>
-      <c r="D147" t="s">
-        <v>173</v>
-      </c>
-      <c r="E147" t="s">
-        <v>9</v>
-      </c>
-      <c r="F147" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>21330051920362</v>
-      </c>
-      <c r="B148" t="s">
-        <v>101</v>
-      </c>
-      <c r="C148" t="s">
-        <v>135</v>
-      </c>
-      <c r="D148" t="s">
-        <v>173</v>
-      </c>
-      <c r="E148" t="s">
-        <v>6</v>
-      </c>
-      <c r="F148" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>21330051920362</v>
-      </c>
-      <c r="B149" t="s">
-        <v>101</v>
-      </c>
-      <c r="C149" t="s">
-        <v>135</v>
-      </c>
-      <c r="D149" t="s">
-        <v>173</v>
-      </c>
-      <c r="E149" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>21330051920362</v>
-      </c>
-      <c r="B150" t="s">
-        <v>101</v>
-      </c>
-      <c r="C150" t="s">
-        <v>135</v>
-      </c>
-      <c r="D150" t="s">
-        <v>173</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>21330051920362</v>
-      </c>
-      <c r="B151" t="s">
-        <v>101</v>
-      </c>
-      <c r="C151" t="s">
-        <v>135</v>
-      </c>
-      <c r="D151" t="s">
-        <v>173</v>
-      </c>
-      <c r="E151" t="s">
-        <v>8</v>
-      </c>
-      <c r="F151" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>21330051920276</v>
-      </c>
-      <c r="B152" t="s">
-        <v>102</v>
-      </c>
-      <c r="C152" t="s">
-        <v>136</v>
-      </c>
-      <c r="D152" t="s">
-        <v>174</v>
-      </c>
-      <c r="E152" t="s">
-        <v>9</v>
-      </c>
-      <c r="F152" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>21330051920276</v>
-      </c>
-      <c r="B153" t="s">
-        <v>102</v>
-      </c>
-      <c r="C153" t="s">
-        <v>136</v>
-      </c>
-      <c r="D153" t="s">
-        <v>174</v>
-      </c>
-      <c r="E153" t="s">
-        <v>6</v>
-      </c>
-      <c r="F153" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>21330051920276</v>
-      </c>
-      <c r="B154" t="s">
-        <v>102</v>
-      </c>
-      <c r="C154" t="s">
-        <v>136</v>
-      </c>
-      <c r="D154" t="s">
-        <v>174</v>
-      </c>
-      <c r="E154" t="s">
-        <v>5</v>
-      </c>
-      <c r="F154" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>21330051920276</v>
-      </c>
-      <c r="B155" t="s">
-        <v>102</v>
-      </c>
-      <c r="C155" t="s">
-        <v>136</v>
-      </c>
-      <c r="D155" t="s">
-        <v>174</v>
-      </c>
-      <c r="E155" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>21330051920276</v>
-      </c>
-      <c r="B156" t="s">
-        <v>102</v>
-      </c>
-      <c r="C156" t="s">
-        <v>136</v>
-      </c>
-      <c r="D156" t="s">
-        <v>174</v>
-      </c>
-      <c r="E156" t="s">
-        <v>8</v>
-      </c>
-      <c r="F156" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>21330051920277</v>
-      </c>
-      <c r="B157" t="s">
-        <v>103</v>
-      </c>
-      <c r="C157" t="s">
-        <v>137</v>
-      </c>
-      <c r="D157" t="s">
-        <v>175</v>
-      </c>
-      <c r="E157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F157" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>21330051920277</v>
-      </c>
-      <c r="B158" t="s">
-        <v>103</v>
-      </c>
-      <c r="C158" t="s">
-        <v>137</v>
-      </c>
-      <c r="D158" t="s">
-        <v>175</v>
-      </c>
-      <c r="E158" t="s">
-        <v>6</v>
-      </c>
-      <c r="F158" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>21330051920277</v>
-      </c>
-      <c r="B159" t="s">
-        <v>103</v>
-      </c>
-      <c r="C159" t="s">
-        <v>137</v>
-      </c>
-      <c r="D159" t="s">
-        <v>175</v>
-      </c>
-      <c r="E159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>21330051920277</v>
-      </c>
-      <c r="B160" t="s">
-        <v>103</v>
-      </c>
-      <c r="C160" t="s">
-        <v>137</v>
-      </c>
-      <c r="D160" t="s">
-        <v>175</v>
-      </c>
-      <c r="E160" t="s">
-        <v>10</v>
-      </c>
-      <c r="F160" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>21330051920277</v>
-      </c>
-      <c r="B161" t="s">
-        <v>103</v>
-      </c>
-      <c r="C161" t="s">
-        <v>137</v>
-      </c>
-      <c r="D161" t="s">
-        <v>175</v>
-      </c>
-      <c r="E161" t="s">
-        <v>8</v>
-      </c>
-      <c r="F161" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>21330051920278</v>
-      </c>
-      <c r="B162" t="s">
-        <v>104</v>
-      </c>
-      <c r="C162" t="s">
-        <v>87</v>
-      </c>
-      <c r="D162" t="s">
-        <v>176</v>
-      </c>
-      <c r="E162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>21330051920278</v>
-      </c>
-      <c r="B163" t="s">
-        <v>104</v>
-      </c>
-      <c r="C163" t="s">
-        <v>87</v>
-      </c>
-      <c r="D163" t="s">
-        <v>176</v>
-      </c>
-      <c r="E163" t="s">
-        <v>6</v>
-      </c>
-      <c r="F163" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>21330051920278</v>
-      </c>
-      <c r="B164" t="s">
-        <v>104</v>
-      </c>
-      <c r="C164" t="s">
-        <v>87</v>
-      </c>
-      <c r="D164" t="s">
-        <v>176</v>
-      </c>
-      <c r="E164" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>21330051920278</v>
-      </c>
-      <c r="B165" t="s">
-        <v>104</v>
-      </c>
-      <c r="C165" t="s">
-        <v>87</v>
-      </c>
-      <c r="D165" t="s">
-        <v>176</v>
-      </c>
-      <c r="E165" t="s">
-        <v>10</v>
-      </c>
-      <c r="F165" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>21330051920278</v>
-      </c>
-      <c r="B166" t="s">
-        <v>104</v>
-      </c>
-      <c r="C166" t="s">
-        <v>87</v>
-      </c>
-      <c r="D166" t="s">
-        <v>176</v>
-      </c>
-      <c r="E166" t="s">
-        <v>8</v>
-      </c>
-      <c r="F166" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>21330051420149</v>
-      </c>
-      <c r="B167" t="s">
-        <v>105</v>
-      </c>
-      <c r="C167" t="s">
-        <v>138</v>
-      </c>
-      <c r="D167" t="s">
-        <v>177</v>
-      </c>
-      <c r="E167" t="s">
-        <v>9</v>
-      </c>
-      <c r="F167" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>21330051420149</v>
-      </c>
-      <c r="B168" t="s">
-        <v>105</v>
-      </c>
-      <c r="C168" t="s">
-        <v>138</v>
-      </c>
-      <c r="D168" t="s">
-        <v>177</v>
-      </c>
-      <c r="E168" t="s">
-        <v>6</v>
-      </c>
-      <c r="F168" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>21330051420149</v>
-      </c>
-      <c r="B169" t="s">
-        <v>105</v>
-      </c>
-      <c r="C169" t="s">
-        <v>138</v>
-      </c>
-      <c r="D169" t="s">
-        <v>177</v>
-      </c>
-      <c r="E169" t="s">
-        <v>5</v>
-      </c>
-      <c r="F169" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>21330051420149</v>
-      </c>
-      <c r="B170" t="s">
-        <v>105</v>
-      </c>
-      <c r="C170" t="s">
-        <v>138</v>
-      </c>
-      <c r="D170" t="s">
-        <v>177</v>
-      </c>
-      <c r="E170" t="s">
-        <v>10</v>
-      </c>
-      <c r="F170" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>21330051420149</v>
-      </c>
-      <c r="B171" t="s">
-        <v>105</v>
-      </c>
-      <c r="C171" t="s">
-        <v>138</v>
-      </c>
-      <c r="D171" t="s">
-        <v>177</v>
-      </c>
-      <c r="E171" t="s">
-        <v>8</v>
-      </c>
-      <c r="F171" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>21330051920279</v>
-      </c>
-      <c r="B172" t="s">
-        <v>106</v>
-      </c>
-      <c r="C172" t="s">
-        <v>139</v>
-      </c>
-      <c r="D172" t="s">
-        <v>178</v>
-      </c>
-      <c r="E172" t="s">
-        <v>9</v>
-      </c>
-      <c r="F172" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>21330051920279</v>
-      </c>
-      <c r="B173" t="s">
-        <v>106</v>
-      </c>
-      <c r="C173" t="s">
-        <v>139</v>
-      </c>
-      <c r="D173" t="s">
-        <v>178</v>
-      </c>
-      <c r="E173" t="s">
-        <v>6</v>
-      </c>
-      <c r="F173" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174">
-        <v>21330051920279</v>
-      </c>
-      <c r="B174" t="s">
-        <v>106</v>
-      </c>
-      <c r="C174" t="s">
-        <v>139</v>
-      </c>
-      <c r="D174" t="s">
-        <v>178</v>
-      </c>
-      <c r="E174" t="s">
-        <v>5</v>
-      </c>
-      <c r="F174" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175">
-        <v>21330051920279</v>
-      </c>
-      <c r="B175" t="s">
-        <v>106</v>
-      </c>
-      <c r="C175" t="s">
-        <v>139</v>
-      </c>
-      <c r="D175" t="s">
-        <v>178</v>
-      </c>
-      <c r="E175" t="s">
-        <v>10</v>
-      </c>
-      <c r="F175" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176">
-        <v>21330051920279</v>
-      </c>
-      <c r="B176" t="s">
-        <v>106</v>
-      </c>
-      <c r="C176" t="s">
-        <v>139</v>
-      </c>
-      <c r="D176" t="s">
-        <v>178</v>
-      </c>
-      <c r="E176" t="s">
-        <v>8</v>
-      </c>
-      <c r="F176" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177">
-        <v>21330051920280</v>
-      </c>
-      <c r="B177" t="s">
-        <v>107</v>
-      </c>
-      <c r="C177" t="s">
-        <v>81</v>
-      </c>
-      <c r="D177" t="s">
-        <v>179</v>
-      </c>
-      <c r="E177" t="s">
-        <v>9</v>
-      </c>
-      <c r="F177" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178">
-        <v>21330051920280</v>
-      </c>
-      <c r="B178" t="s">
-        <v>107</v>
-      </c>
-      <c r="C178" t="s">
-        <v>81</v>
-      </c>
-      <c r="D178" t="s">
-        <v>179</v>
-      </c>
-      <c r="E178" t="s">
-        <v>6</v>
-      </c>
-      <c r="F178" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179">
-        <v>21330051920280</v>
-      </c>
-      <c r="B179" t="s">
-        <v>107</v>
-      </c>
-      <c r="C179" t="s">
-        <v>81</v>
-      </c>
-      <c r="D179" t="s">
-        <v>179</v>
-      </c>
-      <c r="E179" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180">
-        <v>21330051920280</v>
-      </c>
-      <c r="B180" t="s">
-        <v>107</v>
-      </c>
-      <c r="C180" t="s">
-        <v>81</v>
-      </c>
-      <c r="D180" t="s">
-        <v>179</v>
-      </c>
-      <c r="E180" t="s">
-        <v>10</v>
-      </c>
-      <c r="F180" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181">
-        <v>21330051920280</v>
-      </c>
-      <c r="B181" t="s">
-        <v>107</v>
-      </c>
-      <c r="C181" t="s">
-        <v>81</v>
-      </c>
-      <c r="D181" t="s">
-        <v>179</v>
-      </c>
-      <c r="E181" t="s">
-        <v>8</v>
-      </c>
-      <c r="F181" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182">
-        <v>21330051920282</v>
-      </c>
-      <c r="B182" t="s">
-        <v>108</v>
-      </c>
-      <c r="C182" t="s">
-        <v>140</v>
-      </c>
-      <c r="D182" t="s">
-        <v>180</v>
-      </c>
-      <c r="E182" t="s">
-        <v>9</v>
-      </c>
-      <c r="F182" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183">
-        <v>21330051920282</v>
-      </c>
-      <c r="B183" t="s">
-        <v>108</v>
-      </c>
-      <c r="C183" t="s">
-        <v>140</v>
-      </c>
-      <c r="D183" t="s">
-        <v>180</v>
-      </c>
-      <c r="E183" t="s">
-        <v>6</v>
-      </c>
-      <c r="F183" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184">
-        <v>21330051920282</v>
-      </c>
-      <c r="B184" t="s">
-        <v>108</v>
-      </c>
-      <c r="C184" t="s">
-        <v>140</v>
-      </c>
-      <c r="D184" t="s">
-        <v>180</v>
-      </c>
-      <c r="E184" t="s">
-        <v>5</v>
-      </c>
-      <c r="F184" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185">
-        <v>21330051920282</v>
-      </c>
-      <c r="B185" t="s">
-        <v>108</v>
-      </c>
-      <c r="C185" t="s">
-        <v>140</v>
-      </c>
-      <c r="D185" t="s">
-        <v>180</v>
-      </c>
-      <c r="E185" t="s">
-        <v>10</v>
-      </c>
-      <c r="F185" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186">
-        <v>21330051920282</v>
-      </c>
-      <c r="B186" t="s">
-        <v>108</v>
-      </c>
-      <c r="C186" t="s">
-        <v>140</v>
-      </c>
-      <c r="D186" t="s">
-        <v>180</v>
-      </c>
-      <c r="E186" t="s">
-        <v>8</v>
-      </c>
-      <c r="F186" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187">
-        <v>21330051920283</v>
-      </c>
-      <c r="B187" t="s">
-        <v>109</v>
-      </c>
-      <c r="C187" t="s">
-        <v>116</v>
-      </c>
-      <c r="D187" t="s">
-        <v>181</v>
-      </c>
-      <c r="E187" t="s">
-        <v>9</v>
-      </c>
-      <c r="F187" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188">
-        <v>21330051920283</v>
-      </c>
-      <c r="B188" t="s">
-        <v>109</v>
-      </c>
-      <c r="C188" t="s">
-        <v>116</v>
-      </c>
-      <c r="D188" t="s">
-        <v>181</v>
-      </c>
-      <c r="E188" t="s">
-        <v>6</v>
-      </c>
-      <c r="F188" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189">
-        <v>21330051920283</v>
-      </c>
-      <c r="B189" t="s">
-        <v>109</v>
-      </c>
-      <c r="C189" t="s">
-        <v>116</v>
-      </c>
-      <c r="D189" t="s">
-        <v>181</v>
-      </c>
-      <c r="E189" t="s">
-        <v>5</v>
-      </c>
-      <c r="F189" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190">
-        <v>21330051920283</v>
-      </c>
-      <c r="B190" t="s">
-        <v>109</v>
-      </c>
-      <c r="C190" t="s">
-        <v>116</v>
-      </c>
-      <c r="D190" t="s">
-        <v>181</v>
-      </c>
-      <c r="E190" t="s">
-        <v>10</v>
-      </c>
-      <c r="F190" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191">
-        <v>21330051920283</v>
-      </c>
-      <c r="B191" t="s">
-        <v>109</v>
-      </c>
-      <c r="C191" t="s">
-        <v>116</v>
-      </c>
-      <c r="D191" t="s">
-        <v>181</v>
-      </c>
-      <c r="E191" t="s">
-        <v>8</v>
-      </c>
-      <c r="F191" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192">
-        <v>21330051920284</v>
-      </c>
-      <c r="B192" t="s">
-        <v>110</v>
-      </c>
-      <c r="C192" t="s">
-        <v>141</v>
-      </c>
-      <c r="D192" t="s">
-        <v>182</v>
-      </c>
-      <c r="E192" t="s">
-        <v>9</v>
-      </c>
-      <c r="F192" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193">
-        <v>21330051920284</v>
-      </c>
-      <c r="B193" t="s">
-        <v>110</v>
-      </c>
-      <c r="C193" t="s">
-        <v>141</v>
-      </c>
-      <c r="D193" t="s">
-        <v>182</v>
-      </c>
-      <c r="E193" t="s">
-        <v>6</v>
-      </c>
-      <c r="F193" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194">
-        <v>21330051920284</v>
-      </c>
-      <c r="B194" t="s">
-        <v>110</v>
-      </c>
-      <c r="C194" t="s">
-        <v>141</v>
-      </c>
-      <c r="D194" t="s">
-        <v>182</v>
-      </c>
-      <c r="E194" t="s">
-        <v>5</v>
-      </c>
-      <c r="F194" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195">
-        <v>21330051920284</v>
-      </c>
-      <c r="B195" t="s">
-        <v>110</v>
-      </c>
-      <c r="C195" t="s">
-        <v>141</v>
-      </c>
-      <c r="D195" t="s">
-        <v>182</v>
-      </c>
-      <c r="E195" t="s">
-        <v>10</v>
-      </c>
-      <c r="F195" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196">
-        <v>21330051920284</v>
-      </c>
-      <c r="B196" t="s">
-        <v>110</v>
-      </c>
-      <c r="C196" t="s">
-        <v>141</v>
-      </c>
-      <c r="D196" t="s">
-        <v>182</v>
-      </c>
-      <c r="E196" t="s">
-        <v>8</v>
-      </c>
-      <c r="F196" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197">
-        <v>21330051920285</v>
-      </c>
-      <c r="B197" t="s">
-        <v>111</v>
-      </c>
-      <c r="C197" t="s">
-        <v>98</v>
-      </c>
-      <c r="D197" t="s">
-        <v>183</v>
-      </c>
-      <c r="E197" t="s">
-        <v>9</v>
-      </c>
-      <c r="F197" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198">
-        <v>21330051920285</v>
-      </c>
-      <c r="B198" t="s">
-        <v>111</v>
-      </c>
-      <c r="C198" t="s">
-        <v>98</v>
-      </c>
-      <c r="D198" t="s">
-        <v>183</v>
-      </c>
-      <c r="E198" t="s">
-        <v>6</v>
-      </c>
-      <c r="F198" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199">
-        <v>21330051920285</v>
-      </c>
-      <c r="B199" t="s">
-        <v>111</v>
-      </c>
-      <c r="C199" t="s">
-        <v>98</v>
-      </c>
-      <c r="D199" t="s">
-        <v>183</v>
-      </c>
-      <c r="E199" t="s">
-        <v>5</v>
-      </c>
-      <c r="F199" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200">
-        <v>21330051920285</v>
-      </c>
-      <c r="B200" t="s">
-        <v>111</v>
-      </c>
-      <c r="C200" t="s">
-        <v>98</v>
-      </c>
-      <c r="D200" t="s">
-        <v>183</v>
-      </c>
-      <c r="E200" t="s">
-        <v>10</v>
-      </c>
-      <c r="F200" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201">
-        <v>21330051920285</v>
-      </c>
-      <c r="B201" t="s">
-        <v>111</v>
-      </c>
-      <c r="C201" t="s">
-        <v>98</v>
-      </c>
-      <c r="D201" t="s">
-        <v>183</v>
-      </c>
-      <c r="E201" t="s">
-        <v>8</v>
-      </c>
-      <c r="F201" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202">
-        <v>21330051920286</v>
-      </c>
-      <c r="B202" t="s">
-        <v>112</v>
-      </c>
-      <c r="C202" t="s">
-        <v>97</v>
-      </c>
-      <c r="D202" t="s">
-        <v>184</v>
-      </c>
-      <c r="E202" t="s">
-        <v>9</v>
-      </c>
-      <c r="F202" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203">
-        <v>21330051920286</v>
-      </c>
-      <c r="B203" t="s">
-        <v>112</v>
-      </c>
-      <c r="C203" t="s">
-        <v>97</v>
-      </c>
-      <c r="D203" t="s">
-        <v>184</v>
-      </c>
-      <c r="E203" t="s">
-        <v>6</v>
-      </c>
-      <c r="F203" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204">
-        <v>21330051920286</v>
-      </c>
-      <c r="B204" t="s">
-        <v>112</v>
-      </c>
-      <c r="C204" t="s">
-        <v>97</v>
-      </c>
-      <c r="D204" t="s">
-        <v>184</v>
-      </c>
-      <c r="E204" t="s">
-        <v>5</v>
-      </c>
-      <c r="F204" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205">
-        <v>21330051920286</v>
-      </c>
-      <c r="B205" t="s">
-        <v>112</v>
-      </c>
-      <c r="C205" t="s">
-        <v>97</v>
-      </c>
-      <c r="D205" t="s">
-        <v>184</v>
-      </c>
-      <c r="E205" t="s">
-        <v>10</v>
-      </c>
-      <c r="F205" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206">
-        <v>21330051920286</v>
-      </c>
-      <c r="B206" t="s">
-        <v>112</v>
-      </c>
-      <c r="C206" t="s">
-        <v>97</v>
-      </c>
-      <c r="D206" t="s">
-        <v>184</v>
-      </c>
-      <c r="E206" t="s">
-        <v>8</v>
-      </c>
-      <c r="F206" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207">
-        <v>20330051920358</v>
-      </c>
-      <c r="B207" t="s">
-        <v>113</v>
-      </c>
-      <c r="C207" t="s">
-        <v>142</v>
-      </c>
-      <c r="D207" t="s">
-        <v>185</v>
-      </c>
-      <c r="E207" t="s">
-        <v>9</v>
-      </c>
-      <c r="F207" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208">
-        <v>20330051920358</v>
-      </c>
-      <c r="B208" t="s">
-        <v>113</v>
-      </c>
-      <c r="C208" t="s">
-        <v>142</v>
-      </c>
-      <c r="D208" t="s">
-        <v>185</v>
-      </c>
-      <c r="E208" t="s">
-        <v>6</v>
-      </c>
-      <c r="F208" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209">
-        <v>20330051920358</v>
-      </c>
-      <c r="B209" t="s">
-        <v>113</v>
-      </c>
-      <c r="C209" t="s">
-        <v>142</v>
-      </c>
-      <c r="D209" t="s">
-        <v>185</v>
-      </c>
-      <c r="E209" t="s">
-        <v>5</v>
-      </c>
-      <c r="F209" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210">
-        <v>20330051920358</v>
-      </c>
-      <c r="B210" t="s">
-        <v>113</v>
-      </c>
-      <c r="C210" t="s">
-        <v>142</v>
-      </c>
-      <c r="D210" t="s">
-        <v>185</v>
-      </c>
-      <c r="E210" t="s">
-        <v>10</v>
-      </c>
-      <c r="F210" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211">
-        <v>20330051920358</v>
-      </c>
-      <c r="B211" t="s">
-        <v>113</v>
-      </c>
-      <c r="C211" t="s">
-        <v>142</v>
-      </c>
-      <c r="D211" t="s">
-        <v>185</v>
-      </c>
-      <c r="E211" t="s">
-        <v>8</v>
-      </c>
-      <c r="F211" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212">
-        <v>21330051920287</v>
-      </c>
-      <c r="B212" t="s">
-        <v>114</v>
-      </c>
-      <c r="C212" t="s">
-        <v>143</v>
-      </c>
-      <c r="D212" t="s">
-        <v>186</v>
-      </c>
-      <c r="E212" t="s">
-        <v>9</v>
-      </c>
-      <c r="F212" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213">
-        <v>21330051920287</v>
-      </c>
-      <c r="B213" t="s">
-        <v>114</v>
-      </c>
-      <c r="C213" t="s">
-        <v>143</v>
-      </c>
-      <c r="D213" t="s">
-        <v>186</v>
-      </c>
-      <c r="E213" t="s">
-        <v>6</v>
-      </c>
-      <c r="F213" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214">
-        <v>21330051920287</v>
-      </c>
-      <c r="B214" t="s">
-        <v>114</v>
-      </c>
-      <c r="C214" t="s">
-        <v>143</v>
-      </c>
-      <c r="D214" t="s">
-        <v>186</v>
-      </c>
-      <c r="E214" t="s">
-        <v>5</v>
-      </c>
-      <c r="F214" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215">
-        <v>21330051920287</v>
-      </c>
-      <c r="B215" t="s">
-        <v>114</v>
-      </c>
-      <c r="C215" t="s">
-        <v>143</v>
-      </c>
-      <c r="D215" t="s">
-        <v>186</v>
-      </c>
-      <c r="E215" t="s">
-        <v>10</v>
-      </c>
-      <c r="F215" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216">
-        <v>21330051920287</v>
-      </c>
-      <c r="B216" t="s">
-        <v>114</v>
-      </c>
-      <c r="C216" t="s">
-        <v>143</v>
-      </c>
-      <c r="D216" t="s">
-        <v>186</v>
-      </c>
-      <c r="E216" t="s">
-        <v>8</v>
-      </c>
-      <c r="F216" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217">
-        <v>21330051920288</v>
-      </c>
-      <c r="B217" t="s">
-        <v>115</v>
-      </c>
-      <c r="C217" t="s">
-        <v>144</v>
-      </c>
-      <c r="D217" t="s">
-        <v>187</v>
-      </c>
-      <c r="E217" t="s">
-        <v>9</v>
-      </c>
-      <c r="F217" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218">
-        <v>21330051920288</v>
-      </c>
-      <c r="B218" t="s">
-        <v>115</v>
-      </c>
-      <c r="C218" t="s">
-        <v>144</v>
-      </c>
-      <c r="D218" t="s">
-        <v>187</v>
-      </c>
-      <c r="E218" t="s">
-        <v>6</v>
-      </c>
-      <c r="F218" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219">
-        <v>21330051920288</v>
-      </c>
-      <c r="B219" t="s">
-        <v>115</v>
-      </c>
-      <c r="C219" t="s">
-        <v>144</v>
-      </c>
-      <c r="D219" t="s">
-        <v>187</v>
-      </c>
-      <c r="E219" t="s">
-        <v>5</v>
-      </c>
-      <c r="F219" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220">
-        <v>21330051920288</v>
-      </c>
-      <c r="B220" t="s">
-        <v>115</v>
-      </c>
-      <c r="C220" t="s">
-        <v>144</v>
-      </c>
-      <c r="D220" t="s">
-        <v>187</v>
-      </c>
-      <c r="E220" t="s">
-        <v>10</v>
-      </c>
-      <c r="F220" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
-        <v>21330051920288</v>
-      </c>
-      <c r="B221" t="s">
-        <v>115</v>
-      </c>
-      <c r="C221" t="s">
-        <v>144</v>
-      </c>
-      <c r="D221" t="s">
-        <v>187</v>
-      </c>
-      <c r="E221" t="s">
-        <v>8</v>
-      </c>
-      <c r="F221" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -9145,750 +6954,750 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920252</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920253</v>
+        <v>21330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920254</v>
+        <v>21330051920088</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920255</v>
+        <v>21330051920282</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920256</v>
+        <v>21330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920257</v>
+        <v>21330051920255</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920258</v>
+        <v>21330051920262</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920259</v>
+        <v>21330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920260</v>
+        <v>21330051920267</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920261</v>
+        <v>21330051920358</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920262</v>
+        <v>21330051920268</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920263</v>
+        <v>21330051920273</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920264</v>
+        <v>21330051920361</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920265</v>
+        <v>21330051420149</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920266</v>
+        <v>21330051920285</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920267</v>
+        <v>21330051920288</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920087</v>
+        <v>21330051920253</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920088</v>
+        <v>21330051920254</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920358</v>
+        <v>21330051920256</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920268</v>
+        <v>21330051920257</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920091</v>
+        <v>21330051920258</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920270</v>
+        <v>21330051920259</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920271</v>
+        <v>21330051920263</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920272</v>
+        <v>21330051920264</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920273</v>
+        <v>21330051920266</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920274</v>
+        <v>21330051920087</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920361</v>
+        <v>21330051920091</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920275</v>
+        <v>21330051920270</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920362</v>
+        <v>21330051920271</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920276</v>
+        <v>21330051920272</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920277</v>
+        <v>21330051920274</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920278</v>
+        <v>21330051920275</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051420149</v>
+        <v>21330051920362</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920279</v>
+        <v>21330051920276</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920280</v>
+        <v>21330051920277</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920282</v>
+        <v>21330051920278</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920283</v>
+        <v>21330051920279</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920284</v>
+        <v>21330051920280</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920285</v>
+        <v>21330051920283</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920286</v>
+        <v>21330051920284</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>20330051920358</v>
+        <v>21330051920286</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>21330051920287</v>
+        <v>20330051920358</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>21330051920288</v>
+        <v>21330051920287</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9898,7 +7707,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9928,6 +7737,1248 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920253</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920253</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920254</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920256</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920256</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920257</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920258</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920258</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920259</v>
+      </c>
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920263</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920263</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920264</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920264</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920266</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920266</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920087</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920087</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920091</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920091</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920270</v>
+      </c>
+      <c r="B24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920270</v>
+      </c>
+      <c r="B25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920271</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920271</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920272</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920272</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920274</v>
+      </c>
+      <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920274</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920275</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920275</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920362</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920362</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>65</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920276</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920276</v>
+      </c>
+      <c r="B37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920277</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920277</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920278</v>
+      </c>
+      <c r="B40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920278</v>
+      </c>
+      <c r="B41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920279</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920279</v>
+      </c>
+      <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920280</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>179</v>
+      </c>
+      <c r="E44" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920280</v>
+      </c>
+      <c r="B45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" t="s">
+        <v>179</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920283</v>
+      </c>
+      <c r="B46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920283</v>
+      </c>
+      <c r="B47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920284</v>
+      </c>
+      <c r="B48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>21330051920284</v>
+      </c>
+      <c r="B49" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
+        <v>182</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>21330051920286</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>21330051920286</v>
+      </c>
+      <c r="B51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920358</v>
+      </c>
+      <c r="B52" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" t="s">
+        <v>185</v>
+      </c>
+      <c r="E52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920358</v>
+      </c>
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>65</v>
+      </c>
+      <c r="G53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>21330051920287</v>
+      </c>
+      <c r="B54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" t="s">
+        <v>6</v>
+      </c>
+      <c r="F54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>21330051920287</v>
+      </c>
+      <c r="B55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>65</v>
+      </c>
+      <c r="G55">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -215,18 +215,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
@@ -251,57 +251,162 @@
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RUBALCAVA</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BENITO</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YARELI</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DULCE NAOMI</t>
+  </si>
+  <si>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>BRIANDA RENEE</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
     <t>ARGÜELLO</t>
   </si>
   <si>
     <t>CRESCENCIO</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
     <t>MERINO</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -314,12 +419,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -335,27 +434,15 @@
     <t>RUIZ</t>
   </si>
   <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
     <t>TELLEZ</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
     <t>VARGAS</t>
   </si>
   <si>
@@ -365,12 +452,6 @@
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>NARANJO</t>
   </si>
   <si>
@@ -386,33 +467,15 @@
     <t>PETRILLI</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
     <t>SORIANO</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>CADENA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
@@ -422,9 +485,6 @@
     <t>BERNABE</t>
   </si>
   <si>
-    <t>NAVA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -434,15 +494,9 @@
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>ARAUZ</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>ARELLANO</t>
   </si>
   <si>
@@ -452,24 +506,12 @@
     <t>AMECA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>MELANI PAOLA</t>
-  </si>
-  <si>
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
     <t>NADIA</t>
   </si>
   <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
     <t>SUGHEYDI JAZMIN</t>
   </si>
   <si>
@@ -482,39 +524,15 @@
     <t>LESLY JAREDT</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
-  </si>
-  <si>
     <t>VENUS</t>
   </si>
   <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
     <t>BIBIAN YANEL</t>
   </si>
   <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
     <t>EVELIN ALEXANDRA</t>
   </si>
   <si>
-    <t>ANGELINA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
     <t>ANA PAOLA</t>
   </si>
   <si>
@@ -527,15 +545,9 @@
     <t>MILDRED MARIANA</t>
   </si>
   <si>
-    <t>MARIANA PAOLA</t>
-  </si>
-  <si>
     <t>ANGELICA NAOMI</t>
   </si>
   <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
     <t>VIRIDIANA</t>
   </si>
   <si>
@@ -551,27 +563,18 @@
     <t>ARANTXA</t>
   </si>
   <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
     <t>ISAI</t>
   </si>
   <si>
     <t>BETHSABE</t>
   </si>
   <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
     <t>VIANEY</t>
   </si>
   <si>
     <t>RICARDO</t>
   </si>
   <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
     <t>MAGDA SARAY</t>
   </si>
   <si>
@@ -579,9 +582,6 @@
   </si>
   <si>
     <t>EZEQUIEL</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1070,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -1079,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1133,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1147,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -1201,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1224,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1278,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1287,7 +1287,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1310,7 +1310,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>9</v>
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1364,7 +1364,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1378,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -1387,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1455,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -1464,7 +1464,7 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1518,7 +1518,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1532,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1541,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -1586,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1595,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1618,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1663,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1686,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>8</v>
@@ -1740,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1749,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1763,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1772,7 +1772,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -1817,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1826,7 +1826,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1840,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -1849,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -1894,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1903,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1994,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -2003,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -2057,7 +2057,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2071,7 +2071,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -2080,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -2125,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2134,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2148,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2157,7 +2157,7 @@
         <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -2202,7 +2202,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2211,7 +2211,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>-1</v>
@@ -2225,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -2234,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -2279,7 +2279,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2288,7 +2288,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -2311,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>7</v>
@@ -2356,7 +2356,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2365,7 +2365,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2379,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>10</v>
@@ -2388,7 +2388,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>9</v>
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2456,7 +2456,7 @@
         <v>-1</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2465,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -2510,7 +2510,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2519,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>-1</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -2542,7 +2542,7 @@
         <v>7</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2596,7 +2596,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2610,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2619,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -2664,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2687,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>10</v>
@@ -2696,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>8</v>
@@ -2741,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2750,7 +2750,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -2818,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -2850,7 +2850,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -2895,7 +2895,7 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2904,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2918,7 +2918,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>10</v>
@@ -2927,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>9</v>
@@ -2972,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2981,7 +2981,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2995,7 +2995,7 @@
         <v>-1</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>10</v>
@@ -3004,7 +3004,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -3049,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -3058,7 +3058,7 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -3072,7 +3072,7 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -3081,7 +3081,7 @@
         <v>9</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -3126,7 +3126,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3149,7 +3149,7 @@
         <v>9</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3158,7 +3158,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>-1</v>
@@ -3203,7 +3203,7 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3212,7 +3212,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3226,7 +3226,7 @@
         <v>9</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>10</v>
@@ -3235,7 +3235,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>9</v>
@@ -3280,7 +3280,7 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3289,7 +3289,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3303,7 +3303,7 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3312,7 +3312,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>8</v>
@@ -3357,7 +3357,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3366,7 +3366,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -3389,7 +3389,7 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G34">
         <v>9</v>
@@ -3434,7 +3434,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3443,7 +3443,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3457,7 +3457,7 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -3466,7 +3466,7 @@
         <v>9</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3511,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3520,7 +3520,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3534,7 +3534,7 @@
         <v>-1</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
         <v>9</v>
@@ -3543,7 +3543,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G36">
         <v>7</v>
@@ -3588,7 +3588,7 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3597,7 +3597,7 @@
         <v>10</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3611,7 +3611,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -3620,7 +3620,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -3665,7 +3665,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3674,7 +3674,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3688,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -3697,7 +3697,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G38">
         <v>8</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3751,7 +3751,7 @@
         <v>10</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3765,7 +3765,7 @@
         <v>9</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>10</v>
@@ -3774,7 +3774,7 @@
         <v>9</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3819,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3828,7 +3828,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3842,7 +3842,7 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>9</v>
@@ -3851,7 +3851,7 @@
         <v>9</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>8</v>
@@ -3896,7 +3896,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>9</v>
@@ -3905,7 +3905,7 @@
         <v>9</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>8</v>
@@ -3919,7 +3919,7 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -3973,7 +3973,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3996,7 +3996,7 @@
         <v>-1</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -4050,7 +4050,7 @@
         <v>-1</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4059,7 +4059,7 @@
         <v>6</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>6</v>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>9</v>
@@ -4082,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>8</v>
@@ -4127,7 +4127,7 @@
         <v>7</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>9</v>
@@ -4136,7 +4136,7 @@
         <v>9</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4150,7 +4150,7 @@
         <v>9</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>9</v>
@@ -4159,7 +4159,7 @@
         <v>8</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -4204,7 +4204,7 @@
         <v>9</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>9</v>
@@ -4213,7 +4213,7 @@
         <v>8</v>
       </c>
       <c r="X44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y44">
         <v>6</v>
@@ -4227,7 +4227,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>8</v>
@@ -4236,7 +4236,7 @@
         <v>9</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G45">
         <v>7</v>
@@ -4281,7 +4281,7 @@
         <v>6</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V45">
         <v>8</v>
@@ -4290,7 +4290,7 @@
         <v>9</v>
       </c>
       <c r="X45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y45">
         <v>7</v>
@@ -4304,7 +4304,7 @@
         <v>-1</v>
       </c>
       <c r="C46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D46">
         <v>10</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>7</v>
@@ -4358,7 +4358,7 @@
         <v>-1</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V46">
         <v>10</v>
@@ -4367,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="X46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y46">
         <v>7</v>
@@ -4381,7 +4381,7 @@
         <v>7</v>
       </c>
       <c r="C47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D47">
         <v>9</v>
@@ -4390,7 +4390,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G47">
         <v>7</v>
@@ -4435,7 +4435,7 @@
         <v>7</v>
       </c>
       <c r="U47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V47">
         <v>9</v>
@@ -4444,7 +4444,7 @@
         <v>10</v>
       </c>
       <c r="X47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y47">
         <v>7</v>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -4512,27 +4512,30 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.7</v>
+      </c>
       <c r="I2">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4541,27 +4544,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4570,30 +4576,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>72.73</v>
+        <v>95.45</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>27.27</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4602,25 +4608,25 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>77.27</v>
+        <v>97.73</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>22.73</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4694,7 +4700,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4729,13 +4735,13 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -4743,19 +4749,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
@@ -4763,39 +4769,39 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920252</v>
+        <v>21330051920255</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -4803,19 +4809,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920252</v>
+        <v>21330051920260</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -4823,39 +4829,39 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920252</v>
+        <v>21330051920260</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
@@ -4863,39 +4869,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920253</v>
+        <v>21330051920261</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920253</v>
+        <v>21330051920261</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -4903,19 +4909,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920254</v>
+        <v>21330051920261</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -4923,19 +4929,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920254</v>
+        <v>21330051920262</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>66</v>
@@ -4943,19 +4949,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920255</v>
+        <v>21330051920265</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -4963,59 +4969,59 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920255</v>
+        <v>21330051920267</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920255</v>
+        <v>21330051920088</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920256</v>
+        <v>21330051920088</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
@@ -5023,39 +5029,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920256</v>
+        <v>21330051920358</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920257</v>
+        <v>21330051920268</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>65</v>
@@ -5063,19 +5069,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920257</v>
+        <v>21330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
@@ -5083,19 +5089,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920258</v>
+        <v>21330051920361</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>65</v>
@@ -5103,19 +5109,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920258</v>
+        <v>21330051420149</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>66</v>
@@ -5123,39 +5129,39 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920259</v>
+        <v>21330051920282</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920259</v>
+        <v>21330051920282</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
@@ -5163,19 +5169,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920260</v>
+        <v>21330051920282</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>65</v>
@@ -5183,19 +5189,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920260</v>
+        <v>21330051920285</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>66</v>
@@ -5203,1722 +5209,22 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920260</v>
+        <v>21330051920288</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920260</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920261</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920261</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920261</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920261</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920262</v>
-      </c>
-      <c r="B32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920262</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" t="s">
-        <v>156</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920262</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920263</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920263</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920264</v>
-      </c>
-      <c r="B37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>125</v>
-      </c>
-      <c r="D37" t="s">
-        <v>157</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920264</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920265</v>
-      </c>
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>158</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920265</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920265</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>158</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920266</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920266</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" t="s">
-        <v>159</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920267</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" t="s">
-        <v>160</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920267</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>126</v>
-      </c>
-      <c r="D45" t="s">
-        <v>160</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920267</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920087</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" t="s">
-        <v>161</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920087</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" t="s">
-        <v>161</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920088</v>
-      </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>128</v>
-      </c>
-      <c r="D49" t="s">
-        <v>162</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920088</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>128</v>
-      </c>
-      <c r="D50" t="s">
-        <v>162</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920088</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" t="s">
-        <v>128</v>
-      </c>
-      <c r="D51" t="s">
-        <v>162</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920088</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" t="s">
-        <v>162</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920358</v>
-      </c>
-      <c r="B53" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" t="s">
-        <v>129</v>
-      </c>
-      <c r="D53" t="s">
-        <v>163</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920358</v>
-      </c>
-      <c r="B54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" t="s">
-        <v>163</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920358</v>
-      </c>
-      <c r="B55" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" t="s">
-        <v>163</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920268</v>
-      </c>
-      <c r="B56" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" t="s">
-        <v>130</v>
-      </c>
-      <c r="D56" t="s">
-        <v>164</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920268</v>
-      </c>
-      <c r="B57" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" t="s">
-        <v>164</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920268</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>130</v>
-      </c>
-      <c r="D58" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920091</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920091</v>
-      </c>
-      <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920270</v>
-      </c>
-      <c r="B61" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" t="s">
-        <v>131</v>
-      </c>
-      <c r="D61" t="s">
-        <v>166</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920270</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62" t="s">
-        <v>166</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920271</v>
-      </c>
-      <c r="B63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" t="s">
-        <v>132</v>
-      </c>
-      <c r="D63" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920271</v>
-      </c>
-      <c r="B64" t="s">
-        <v>96</v>
-      </c>
-      <c r="C64" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64" t="s">
-        <v>167</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920272</v>
-      </c>
-      <c r="B65" t="s">
-        <v>97</v>
-      </c>
-      <c r="C65" t="s">
-        <v>133</v>
-      </c>
-      <c r="D65" t="s">
-        <v>168</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920272</v>
-      </c>
-      <c r="B66" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" t="s">
-        <v>133</v>
-      </c>
-      <c r="D66" t="s">
-        <v>168</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920273</v>
-      </c>
-      <c r="B67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" t="s">
-        <v>169</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920273</v>
-      </c>
-      <c r="B68" t="s">
-        <v>98</v>
-      </c>
-      <c r="C68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D68" t="s">
-        <v>169</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920273</v>
-      </c>
-      <c r="B69" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" t="s">
-        <v>134</v>
-      </c>
-      <c r="D69" t="s">
-        <v>169</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920274</v>
-      </c>
-      <c r="B70" t="s">
-        <v>99</v>
-      </c>
-      <c r="C70" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" t="s">
-        <v>170</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920274</v>
-      </c>
-      <c r="B71" t="s">
-        <v>99</v>
-      </c>
-      <c r="C71" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920361</v>
-      </c>
-      <c r="B72" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" t="s">
-        <v>107</v>
-      </c>
-      <c r="D72" t="s">
-        <v>171</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920361</v>
-      </c>
-      <c r="B73" t="s">
-        <v>99</v>
-      </c>
-      <c r="C73" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920361</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920275</v>
-      </c>
-      <c r="B75" t="s">
-        <v>100</v>
-      </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
-        <v>172</v>
-      </c>
-      <c r="E75" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920275</v>
-      </c>
-      <c r="B76" t="s">
-        <v>100</v>
-      </c>
-      <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="s">
-        <v>172</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920362</v>
-      </c>
-      <c r="B77" t="s">
-        <v>101</v>
-      </c>
-      <c r="C77" t="s">
-        <v>135</v>
-      </c>
-      <c r="D77" t="s">
-        <v>173</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920362</v>
-      </c>
-      <c r="B78" t="s">
-        <v>101</v>
-      </c>
-      <c r="C78" t="s">
-        <v>135</v>
-      </c>
-      <c r="D78" t="s">
-        <v>173</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920276</v>
-      </c>
-      <c r="B79" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" t="s">
-        <v>136</v>
-      </c>
-      <c r="D79" t="s">
-        <v>174</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920276</v>
-      </c>
-      <c r="B80" t="s">
-        <v>102</v>
-      </c>
-      <c r="C80" t="s">
-        <v>136</v>
-      </c>
-      <c r="D80" t="s">
-        <v>174</v>
-      </c>
-      <c r="E80" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920277</v>
-      </c>
-      <c r="B81" t="s">
-        <v>103</v>
-      </c>
-      <c r="C81" t="s">
-        <v>137</v>
-      </c>
-      <c r="D81" t="s">
-        <v>175</v>
-      </c>
-      <c r="E81" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920277</v>
-      </c>
-      <c r="B82" t="s">
-        <v>103</v>
-      </c>
-      <c r="C82" t="s">
-        <v>137</v>
-      </c>
-      <c r="D82" t="s">
-        <v>175</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920278</v>
-      </c>
-      <c r="B83" t="s">
-        <v>104</v>
-      </c>
-      <c r="C83" t="s">
-        <v>87</v>
-      </c>
-      <c r="D83" t="s">
-        <v>176</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920278</v>
-      </c>
-      <c r="B84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C84" t="s">
-        <v>87</v>
-      </c>
-      <c r="D84" t="s">
-        <v>176</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051420149</v>
-      </c>
-      <c r="B85" t="s">
-        <v>105</v>
-      </c>
-      <c r="C85" t="s">
-        <v>138</v>
-      </c>
-      <c r="D85" t="s">
-        <v>177</v>
-      </c>
-      <c r="E85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051420149</v>
-      </c>
-      <c r="B86" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86" t="s">
-        <v>138</v>
-      </c>
-      <c r="D86" t="s">
-        <v>177</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051420149</v>
-      </c>
-      <c r="B87" t="s">
-        <v>105</v>
-      </c>
-      <c r="C87" t="s">
-        <v>138</v>
-      </c>
-      <c r="D87" t="s">
-        <v>177</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920279</v>
-      </c>
-      <c r="B88" t="s">
-        <v>106</v>
-      </c>
-      <c r="C88" t="s">
-        <v>139</v>
-      </c>
-      <c r="D88" t="s">
-        <v>178</v>
-      </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920279</v>
-      </c>
-      <c r="B89" t="s">
-        <v>106</v>
-      </c>
-      <c r="C89" t="s">
-        <v>139</v>
-      </c>
-      <c r="D89" t="s">
-        <v>178</v>
-      </c>
-      <c r="E89" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920280</v>
-      </c>
-      <c r="B90" t="s">
-        <v>107</v>
-      </c>
-      <c r="C90" t="s">
-        <v>81</v>
-      </c>
-      <c r="D90" t="s">
-        <v>179</v>
-      </c>
-      <c r="E90" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920280</v>
-      </c>
-      <c r="B91" t="s">
-        <v>107</v>
-      </c>
-      <c r="C91" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" t="s">
-        <v>179</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920282</v>
-      </c>
-      <c r="B92" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" t="s">
-        <v>140</v>
-      </c>
-      <c r="D92" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920282</v>
-      </c>
-      <c r="B93" t="s">
-        <v>108</v>
-      </c>
-      <c r="C93" t="s">
-        <v>140</v>
-      </c>
-      <c r="D93" t="s">
-        <v>180</v>
-      </c>
-      <c r="E93" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920282</v>
-      </c>
-      <c r="B94" t="s">
-        <v>108</v>
-      </c>
-      <c r="C94" t="s">
-        <v>140</v>
-      </c>
-      <c r="D94" t="s">
-        <v>180</v>
-      </c>
-      <c r="E94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920282</v>
-      </c>
-      <c r="B95" t="s">
-        <v>108</v>
-      </c>
-      <c r="C95" t="s">
-        <v>140</v>
-      </c>
-      <c r="D95" t="s">
-        <v>180</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920283</v>
-      </c>
-      <c r="B96" t="s">
-        <v>109</v>
-      </c>
-      <c r="C96" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" t="s">
-        <v>181</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920283</v>
-      </c>
-      <c r="B97" t="s">
-        <v>109</v>
-      </c>
-      <c r="C97" t="s">
-        <v>116</v>
-      </c>
-      <c r="D97" t="s">
-        <v>181</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920284</v>
-      </c>
-      <c r="B98" t="s">
-        <v>110</v>
-      </c>
-      <c r="C98" t="s">
-        <v>141</v>
-      </c>
-      <c r="D98" t="s">
-        <v>182</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920284</v>
-      </c>
-      <c r="B99" t="s">
-        <v>110</v>
-      </c>
-      <c r="C99" t="s">
-        <v>141</v>
-      </c>
-      <c r="D99" t="s">
-        <v>182</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920285</v>
-      </c>
-      <c r="B100" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" t="s">
-        <v>98</v>
-      </c>
-      <c r="D100" t="s">
-        <v>183</v>
-      </c>
-      <c r="E100" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920285</v>
-      </c>
-      <c r="B101" t="s">
-        <v>111</v>
-      </c>
-      <c r="C101" t="s">
-        <v>98</v>
-      </c>
-      <c r="D101" t="s">
-        <v>183</v>
-      </c>
-      <c r="E101" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920285</v>
-      </c>
-      <c r="B102" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" t="s">
-        <v>98</v>
-      </c>
-      <c r="D102" t="s">
-        <v>183</v>
-      </c>
-      <c r="E102" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920286</v>
-      </c>
-      <c r="B103" t="s">
-        <v>112</v>
-      </c>
-      <c r="C103" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103" t="s">
-        <v>184</v>
-      </c>
-      <c r="E103" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920286</v>
-      </c>
-      <c r="B104" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" t="s">
-        <v>97</v>
-      </c>
-      <c r="D104" t="s">
-        <v>184</v>
-      </c>
-      <c r="E104" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920358</v>
-      </c>
-      <c r="B105" t="s">
-        <v>113</v>
-      </c>
-      <c r="C105" t="s">
-        <v>142</v>
-      </c>
-      <c r="D105" t="s">
-        <v>185</v>
-      </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920358</v>
-      </c>
-      <c r="B106" t="s">
-        <v>113</v>
-      </c>
-      <c r="C106" t="s">
-        <v>142</v>
-      </c>
-      <c r="D106" t="s">
-        <v>185</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920287</v>
-      </c>
-      <c r="B107" t="s">
-        <v>114</v>
-      </c>
-      <c r="C107" t="s">
-        <v>143</v>
-      </c>
-      <c r="D107" t="s">
-        <v>186</v>
-      </c>
-      <c r="E107" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920287</v>
-      </c>
-      <c r="B108" t="s">
-        <v>114</v>
-      </c>
-      <c r="C108" t="s">
-        <v>143</v>
-      </c>
-      <c r="D108" t="s">
-        <v>186</v>
-      </c>
-      <c r="E108" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920288</v>
-      </c>
-      <c r="B109" t="s">
-        <v>115</v>
-      </c>
-      <c r="C109" t="s">
-        <v>144</v>
-      </c>
-      <c r="D109" t="s">
-        <v>187</v>
-      </c>
-      <c r="E109" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920288</v>
-      </c>
-      <c r="B110" t="s">
-        <v>115</v>
-      </c>
-      <c r="C110" t="s">
-        <v>144</v>
-      </c>
-      <c r="D110" t="s">
-        <v>187</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920288</v>
-      </c>
-      <c r="B111" t="s">
-        <v>115</v>
-      </c>
-      <c r="C111" t="s">
-        <v>144</v>
-      </c>
-      <c r="D111" t="s">
-        <v>187</v>
-      </c>
-      <c r="E111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -6954,16 +5260,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -6971,70 +5277,70 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920260</v>
+        <v>21330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920261</v>
+        <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920088</v>
+        <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920282</v>
+        <v>21330051920088</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7045,13 +5351,13 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7059,16 +5365,16 @@
         <v>21330051920255</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7076,16 +5382,16 @@
         <v>21330051920262</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7093,16 +5399,16 @@
         <v>21330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7110,16 +5416,16 @@
         <v>21330051920267</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7127,16 +5433,16 @@
         <v>21330051920358</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7144,16 +5450,16 @@
         <v>21330051920268</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7161,16 +5467,16 @@
         <v>21330051920273</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7178,16 +5484,16 @@
         <v>21330051920361</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7195,16 +5501,16 @@
         <v>21330051420149</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7212,16 +5518,16 @@
         <v>21330051920285</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7229,16 +5535,16 @@
         <v>21330051920288</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7246,16 +5552,16 @@
         <v>21330051920253</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7263,16 +5569,16 @@
         <v>21330051920254</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7280,16 +5586,16 @@
         <v>21330051920256</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7297,16 +5603,16 @@
         <v>21330051920257</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7314,16 +5620,16 @@
         <v>21330051920258</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7331,16 +5637,16 @@
         <v>21330051920259</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7348,16 +5654,16 @@
         <v>21330051920263</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7365,16 +5671,16 @@
         <v>21330051920264</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7382,16 +5688,16 @@
         <v>21330051920266</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7399,16 +5705,16 @@
         <v>21330051920087</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7416,16 +5722,16 @@
         <v>21330051920091</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7433,16 +5739,16 @@
         <v>21330051920270</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7450,16 +5756,16 @@
         <v>21330051920271</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7467,16 +5773,16 @@
         <v>21330051920272</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7484,16 +5790,16 @@
         <v>21330051920274</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7501,16 +5807,16 @@
         <v>21330051920275</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7518,16 +5824,16 @@
         <v>21330051920362</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7535,16 +5841,16 @@
         <v>21330051920276</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7552,16 +5858,16 @@
         <v>21330051920277</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7569,16 +5875,16 @@
         <v>21330051920278</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -7586,16 +5892,16 @@
         <v>21330051920279</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7603,16 +5909,16 @@
         <v>21330051920280</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -7620,16 +5926,16 @@
         <v>21330051920283</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7637,16 +5943,16 @@
         <v>21330051920284</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -7654,16 +5960,16 @@
         <v>21330051920286</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -7671,16 +5977,16 @@
         <v>20330051920358</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7688,16 +5994,16 @@
         <v>21330051920287</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7707,7 +6013,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7739,19 +6045,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920253</v>
+        <v>21330051920252</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -7762,19 +6068,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920253</v>
+        <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -7785,19 +6091,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920254</v>
+        <v>21330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -7808,19 +6114,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920254</v>
+        <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -7831,19 +6137,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920256</v>
+        <v>21330051920088</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -7854,19 +6160,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920256</v>
+        <v>21330051920088</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -7877,22 +6183,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920257</v>
+        <v>21330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -7900,19 +6206,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920257</v>
+        <v>21330051920255</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
@@ -7923,19 +6229,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920258</v>
+        <v>21330051920262</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -7946,19 +6252,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920258</v>
+        <v>21330051920265</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
@@ -7969,22 +6275,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920259</v>
+        <v>21330051920267</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -7992,19 +6298,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920259</v>
+        <v>21330051920358</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -8015,22 +6321,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920263</v>
+        <v>21330051920268</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -8038,22 +6344,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920263</v>
+        <v>21330051920273</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -8061,22 +6367,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920264</v>
+        <v>21330051920361</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -8084,22 +6390,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920264</v>
+        <v>21330051420149</v>
       </c>
       <c r="B17" t="s">
         <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -8107,19 +6413,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920266</v>
+        <v>21330051920285</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>66</v>
@@ -8130,852 +6436,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920266</v>
+        <v>21330051920288</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920087</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" t="s">
-        <v>161</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920087</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920091</v>
-      </c>
-      <c r="B22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920091</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>165</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920270</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920270</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" t="s">
-        <v>166</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920271</v>
-      </c>
-      <c r="B26" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920271</v>
-      </c>
-      <c r="B27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" t="s">
-        <v>167</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920272</v>
-      </c>
-      <c r="B28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920272</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" t="s">
-        <v>168</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920274</v>
-      </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920274</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920275</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920275</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920362</v>
-      </c>
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920362</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920276</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920276</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" t="s">
-        <v>174</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920277</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" t="s">
-        <v>175</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920277</v>
-      </c>
-      <c r="B39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" t="s">
-        <v>175</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920278</v>
-      </c>
-      <c r="B40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920278</v>
-      </c>
-      <c r="B41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920279</v>
-      </c>
-      <c r="B42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>139</v>
-      </c>
-      <c r="D42" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920279</v>
-      </c>
-      <c r="B43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D43" t="s">
-        <v>178</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920280</v>
-      </c>
-      <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" t="s">
-        <v>179</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>66</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920280</v>
-      </c>
-      <c r="B45" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" t="s">
-        <v>179</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920283</v>
-      </c>
-      <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" t="s">
-        <v>181</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920283</v>
-      </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920284</v>
-      </c>
-      <c r="B48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" t="s">
-        <v>141</v>
-      </c>
-      <c r="D48" t="s">
-        <v>182</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920284</v>
-      </c>
-      <c r="B49" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" t="s">
-        <v>141</v>
-      </c>
-      <c r="D49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920286</v>
-      </c>
-      <c r="B50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" t="s">
-        <v>184</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920286</v>
-      </c>
-      <c r="B51" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>20330051920358</v>
-      </c>
-      <c r="B52" t="s">
-        <v>113</v>
-      </c>
-      <c r="C52" t="s">
-        <v>142</v>
-      </c>
-      <c r="D52" t="s">
-        <v>185</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>66</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>20330051920358</v>
-      </c>
-      <c r="B53" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" t="s">
-        <v>142</v>
-      </c>
-      <c r="D53" t="s">
-        <v>185</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>65</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>21330051920287</v>
-      </c>
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" t="s">
-        <v>143</v>
-      </c>
-      <c r="D54" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-      <c r="G54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55">
-        <v>21330051920287</v>
-      </c>
-      <c r="B55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" t="s">
-        <v>143</v>
-      </c>
-      <c r="D55" t="s">
-        <v>186</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>65</v>
-      </c>
-      <c r="G55">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -98,9 +98,6 @@
     <t>JIMENEZ CORTES VENUS</t>
   </si>
   <si>
-    <t>MADRAZO 0 ANGELO RENE</t>
-  </si>
-  <si>
     <t>MARTINEZ GARCIA RICARDO ABEL</t>
   </si>
   <si>
@@ -215,21 +212,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
@@ -245,19 +242,115 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RUBALCAVA</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
+    <t>ANGELINA</t>
+  </si>
+  <si>
+    <t>MARIANA PAOLA</t>
+  </si>
+  <si>
+    <t>BRIANDA RENEE</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NANCY PAOLA</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>ALDUCIN</t>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -266,7 +359,7 @@
     <t>MADRAZO</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
+    <t>MERINO</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -275,43 +368,79 @@
     <t>NAVARRO</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>RUBALCAVA</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
   </si>
   <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ARCADIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PETRILLI</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CADENA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
@@ -320,43 +449,73 @@
     <t>BENITO</t>
   </si>
   <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>ARAUZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AMECA</t>
   </si>
   <si>
     <t>YARELI</t>
   </si>
   <si>
-    <t>MELANI PAOLA</t>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>ANA LILIANA</t>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EMILIANO</t>
+  </si>
+  <si>
+    <t>LESLY JAREDT</t>
+  </si>
+  <si>
+    <t>VENUS</t>
   </si>
   <si>
     <t>RICARDO ABEL</t>
   </si>
   <si>
+    <t>BIBIAN YANEL</t>
+  </si>
+  <si>
     <t>ANGELO RENE</t>
   </si>
   <si>
-    <t>ANGELINA</t>
+    <t>EVELIN ALEXANDRA</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -365,187 +524,22 @@
     <t>DULCE NAOMI</t>
   </si>
   <si>
-    <t>MARIANA PAOLA</t>
+    <t>ANA PAOLA</t>
+  </si>
+  <si>
+    <t>ALYN</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>MILDRED MARIANA</t>
+  </si>
+  <si>
+    <t>ANGELICA NAOMI</t>
   </si>
   <si>
     <t>DUILIO</t>
-  </si>
-  <si>
-    <t>BRIANDA RENEE</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
   </si>
   <si>
     <t>VIRIDIANA</t>
@@ -939,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1082,16 +1076,16 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1100,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1127,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1136,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1159,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1177,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1204,7 +1198,7 @@
         <v>6</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1213,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1242,10 +1236,10 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1254,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1290,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1319,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1331,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1367,7 +1361,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1396,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1408,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1432,7 +1426,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1444,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1467,16 +1461,16 @@
         <v>7</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1485,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1509,10 +1503,10 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1521,7 +1515,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1550,10 +1544,10 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1562,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1586,10 +1580,10 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1598,7 +1592,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1627,10 +1621,10 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1639,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1663,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1675,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1704,10 +1698,10 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1716,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1740,7 +1734,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1752,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1781,10 +1775,10 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1793,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1829,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1852,16 +1846,16 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1870,7 +1864,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1894,10 +1888,10 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1906,7 +1900,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1917,7 +1911,7 @@
         <v>-1</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1929,13 +1923,13 @@
         <v>-1</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1947,7 +1941,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1971,7 +1965,7 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1983,7 +1977,7 @@
         <v>-1</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2012,10 +2006,10 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2024,7 +2018,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2048,10 +2042,10 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2089,10 +2083,10 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2101,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2125,10 +2119,10 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2148,28 +2142,28 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2178,7 +2172,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2202,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2211,10 +2205,10 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2225,28 +2219,28 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H19">
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2255,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2279,19 +2273,19 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2299,31 +2293,31 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>10</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2332,7 +2326,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2353,22 +2347,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2376,31 +2370,31 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2409,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2430,22 +2424,22 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2453,13 +2447,13 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2468,16 +2462,16 @@
         <v>6</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2486,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2507,13 +2501,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2522,7 +2516,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2530,31 +2524,31 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2563,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2584,22 +2578,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2610,28 +2604,28 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>10</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2640,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2664,19 +2658,19 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2684,7 +2678,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2699,16 +2693,16 @@
         <v>10</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25">
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2717,7 +2711,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2738,7 +2732,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2753,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2761,10 +2755,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -2773,16 +2767,16 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H26">
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2794,7 +2788,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2815,10 +2809,10 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2827,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2838,10 +2832,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -2850,19 +2844,19 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2871,7 +2865,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2892,10 +2886,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2904,10 +2898,10 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2915,10 +2909,10 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>10</v>
@@ -2927,19 +2921,19 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2948,7 +2942,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2969,10 +2963,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2981,10 +2975,10 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2992,7 +2986,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -3001,22 +2995,22 @@
         <v>10</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3025,7 +3019,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3046,22 +3040,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>10</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3069,31 +3063,31 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>7</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3102,7 +3096,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3123,22 +3117,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3149,28 +3143,28 @@
         <v>9</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3179,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3203,19 +3197,19 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3223,31 +3217,31 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>10</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3256,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3277,16 +3271,16 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3300,7 +3294,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>8</v>
@@ -3309,22 +3303,22 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3333,7 +3327,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3354,22 +3348,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>8</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3377,10 +3371,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -3389,19 +3383,19 @@
         <v>9</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H34">
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3410,7 +3404,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3431,10 +3425,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>10</v>
@@ -3443,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3454,31 +3448,31 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H35">
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3487,7 +3481,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3508,22 +3502,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3531,31 +3525,31 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>10</v>
       </c>
       <c r="F36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H36">
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3564,7 +3558,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3585,22 +3579,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3611,7 +3605,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -3620,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37">
         <v>8</v>
@@ -3629,10 +3623,10 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3641,7 +3635,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3665,7 +3659,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3674,10 +3668,10 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3694,10 +3688,10 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>8</v>
@@ -3706,10 +3700,10 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3718,7 +3712,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3748,13 +3742,13 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3765,16 +3759,16 @@
         <v>9</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39">
         <v>9</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3783,10 +3777,10 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3795,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3819,19 +3813,19 @@
         <v>9</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>9</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3839,41 +3833,41 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40">
+        <v>-1</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40">
+        <v>-1</v>
+      </c>
+      <c r="I40">
+        <v>7</v>
+      </c>
+      <c r="J40">
+        <v>7</v>
+      </c>
+      <c r="K40">
+        <v>-1</v>
+      </c>
+      <c r="L40">
+        <v>-1</v>
+      </c>
+      <c r="M40">
         <v>6</v>
       </c>
-      <c r="G40">
-        <v>8</v>
-      </c>
-      <c r="H40">
-        <v>-1</v>
-      </c>
-      <c r="I40">
-        <v>-1</v>
-      </c>
-      <c r="J40">
-        <v>-1</v>
-      </c>
-      <c r="K40">
-        <v>-1</v>
-      </c>
-      <c r="L40">
-        <v>-1</v>
-      </c>
-      <c r="M40">
-        <v>-1</v>
-      </c>
       <c r="N40">
         <v>-1</v>
       </c>
@@ -3893,22 +3887,22 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3919,7 +3913,7 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -3928,19 +3922,19 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H41">
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -3949,7 +3943,7 @@
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3973,7 +3967,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3982,10 +3976,10 @@
         <v>6</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3993,31 +3987,31 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>8</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H42">
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -4026,7 +4020,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4047,22 +4041,22 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>8</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4070,7 +4064,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>8</v>
@@ -4079,22 +4073,22 @@
         <v>9</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H43">
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
         <v>-1</v>
@@ -4103,7 +4097,7 @@
         <v>-1</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4124,19 +4118,19 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>8</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4147,76 +4141,76 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44">
         <v>9</v>
       </c>
       <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>-1</v>
+      </c>
+      <c r="I44">
+        <v>8</v>
+      </c>
+      <c r="J44">
+        <v>7</v>
+      </c>
+      <c r="K44">
+        <v>-1</v>
+      </c>
+      <c r="L44">
+        <v>-1</v>
+      </c>
+      <c r="M44">
+        <v>9</v>
+      </c>
+      <c r="N44">
+        <v>-1</v>
+      </c>
+      <c r="O44">
+        <v>-1</v>
+      </c>
+      <c r="P44">
+        <v>-1</v>
+      </c>
+      <c r="Q44">
+        <v>-1</v>
+      </c>
+      <c r="R44">
+        <v>-1</v>
+      </c>
+      <c r="S44">
+        <v>-1</v>
+      </c>
+      <c r="T44">
         <v>6</v>
       </c>
-      <c r="H44">
-        <v>-1</v>
-      </c>
-      <c r="I44">
-        <v>-1</v>
-      </c>
-      <c r="J44">
-        <v>-1</v>
-      </c>
-      <c r="K44">
-        <v>-1</v>
-      </c>
-      <c r="L44">
-        <v>-1</v>
-      </c>
-      <c r="M44">
-        <v>-1</v>
-      </c>
-      <c r="N44">
-        <v>-1</v>
-      </c>
-      <c r="O44">
-        <v>-1</v>
-      </c>
-      <c r="P44">
-        <v>-1</v>
-      </c>
-      <c r="Q44">
-        <v>-1</v>
-      </c>
-      <c r="R44">
-        <v>-1</v>
-      </c>
-      <c r="S44">
-        <v>-1</v>
-      </c>
-      <c r="T44">
-        <v>9</v>
-      </c>
       <c r="U44">
         <v>8</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>9</v>
       </c>
       <c r="Y44">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4224,19 +4218,19 @@
         <v>53</v>
       </c>
       <c r="B45">
+        <v>-1</v>
+      </c>
+      <c r="C45">
         <v>6</v>
       </c>
-      <c r="C45">
-        <v>7</v>
-      </c>
       <c r="D45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G45">
         <v>7</v>
@@ -4245,10 +4239,10 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K45">
         <v>-1</v>
@@ -4257,7 +4251,7 @@
         <v>-1</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4278,22 +4272,22 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="U45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V45">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y45">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4301,20 +4295,20 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C46">
+        <v>9</v>
+      </c>
+      <c r="D46">
+        <v>9</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
         <v>6</v>
       </c>
-      <c r="D46">
-        <v>10</v>
-      </c>
-      <c r="E46">
-        <v>10</v>
-      </c>
-      <c r="F46">
-        <v>10</v>
-      </c>
       <c r="G46">
         <v>7</v>
       </c>
@@ -4322,7 +4316,7 @@
         <v>-1</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J46">
         <v>-1</v>
@@ -4334,7 +4328,7 @@
         <v>-1</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4355,99 +4349,22 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U46">
+        <v>9</v>
+      </c>
+      <c r="V46">
+        <v>9</v>
+      </c>
+      <c r="W46">
+        <v>10</v>
+      </c>
+      <c r="X46">
         <v>6</v>
       </c>
-      <c r="V46">
-        <v>10</v>
-      </c>
-      <c r="W46">
-        <v>10</v>
-      </c>
-      <c r="X46">
-        <v>10</v>
-      </c>
       <c r="Y46">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47">
-        <v>7</v>
-      </c>
-      <c r="C47">
-        <v>9</v>
-      </c>
-      <c r="D47">
-        <v>9</v>
-      </c>
-      <c r="E47">
-        <v>10</v>
-      </c>
-      <c r="F47">
         <v>6</v>
-      </c>
-      <c r="G47">
-        <v>7</v>
-      </c>
-      <c r="H47">
-        <v>-1</v>
-      </c>
-      <c r="I47">
-        <v>-1</v>
-      </c>
-      <c r="J47">
-        <v>-1</v>
-      </c>
-      <c r="K47">
-        <v>-1</v>
-      </c>
-      <c r="L47">
-        <v>-1</v>
-      </c>
-      <c r="M47">
-        <v>-1</v>
-      </c>
-      <c r="N47">
-        <v>-1</v>
-      </c>
-      <c r="O47">
-        <v>-1</v>
-      </c>
-      <c r="P47">
-        <v>-1</v>
-      </c>
-      <c r="Q47">
-        <v>-1</v>
-      </c>
-      <c r="R47">
-        <v>-1</v>
-      </c>
-      <c r="S47">
-        <v>-1</v>
-      </c>
-      <c r="T47">
-        <v>7</v>
-      </c>
-      <c r="U47">
-        <v>9</v>
-      </c>
-      <c r="V47">
-        <v>9</v>
-      </c>
-      <c r="W47">
-        <v>10</v>
-      </c>
-      <c r="X47">
-        <v>6</v>
-      </c>
-      <c r="Y47">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4474,95 +4391,95 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2">
         <v>44</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>72.73</v>
+        <v>77.27</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>27.27</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>44</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>88.64</v>
+      </c>
+      <c r="G3">
+        <v>11.36</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>77.27</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>22.73</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4570,7 +4487,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>44</v>
@@ -4599,42 +4516,42 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>44</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>44</v>
@@ -4652,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4666,7 +4583,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>44</v>
@@ -4700,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4709,16 +4626,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4729,179 +4646,179 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920251</v>
+        <v>21330051920252</v>
       </c>
       <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>91</v>
       </c>
-      <c r="D2" t="s">
-        <v>104</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920252</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920255</v>
+        <v>21330051920261</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920260</v>
+        <v>21330051920262</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920260</v>
+        <v>21330051920088</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920261</v>
+        <v>21330051920273</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920261</v>
+        <v>21330051420149</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920261</v>
+        <v>21330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -4909,322 +4826,62 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920261</v>
+        <v>21330051920282</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920262</v>
+        <v>21330051920285</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920265</v>
+        <v>21330051920288</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920267</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920088</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920088</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920358</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920268</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920273</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920361</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051420149</v>
-      </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920282</v>
-      </c>
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920282</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920282</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920285</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920288</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5243,19 +4900,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5263,16 +4920,16 @@
         <v>21330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
-        <v>108</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5280,16 +4937,16 @@
         <v>21330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5297,16 +4954,16 @@
         <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5314,47 +4971,47 @@
         <v>21330051920260</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>21330051920262</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920251</v>
+        <v>21330051920088</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5362,16 +5019,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920255</v>
+        <v>21330051920273</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5379,16 +5036,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920262</v>
+        <v>21330051420149</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5396,16 +5053,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920265</v>
+        <v>21330051920285</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5413,16 +5070,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920267</v>
+        <v>21330051920288</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5430,135 +5087,135 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920358</v>
+        <v>21330051920251</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920268</v>
+        <v>21330051920253</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920273</v>
+        <v>21330051920254</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920361</v>
+        <v>21330051920255</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051420149</v>
+        <v>21330051920256</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920285</v>
+        <v>21330051920257</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920288</v>
+        <v>21330051920258</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920253</v>
+        <v>21330051920259</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5566,16 +5223,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920254</v>
+        <v>21330051920263</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5583,16 +5240,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920256</v>
+        <v>21330051920264</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5600,16 +5257,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920257</v>
+        <v>21330051920265</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5617,16 +5274,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920258</v>
+        <v>21330051920266</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5634,16 +5291,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920259</v>
+        <v>21330051920267</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5651,16 +5305,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920263</v>
+        <v>21330051920087</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5668,16 +5322,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920264</v>
+        <v>21330051920358</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5685,16 +5339,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920266</v>
+        <v>21330051920268</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5702,16 +5356,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920087</v>
+        <v>21330051920091</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5719,16 +5373,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920091</v>
+        <v>21330051920270</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5736,16 +5390,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920270</v>
+        <v>21330051920271</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5753,16 +5407,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920271</v>
+        <v>21330051920272</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5770,16 +5424,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920272</v>
+        <v>21330051920274</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5787,16 +5441,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920274</v>
+        <v>21330051920361</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5807,13 +5461,13 @@
         <v>21330051920275</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5824,13 +5478,13 @@
         <v>21330051920362</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5841,13 +5495,13 @@
         <v>21330051920276</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5858,13 +5512,13 @@
         <v>21330051920277</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5875,13 +5529,13 @@
         <v>21330051920278</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5892,13 +5546,13 @@
         <v>21330051920279</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5909,13 +5563,13 @@
         <v>21330051920280</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5926,13 +5580,13 @@
         <v>21330051920283</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5943,13 +5597,13 @@
         <v>21330051920284</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5960,13 +5614,13 @@
         <v>21330051920286</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -5977,13 +5631,13 @@
         <v>20330051920358</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -5994,13 +5648,13 @@
         <v>21330051920287</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -6013,7 +5667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6022,22 +5676,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6048,19 +5702,19 @@
         <v>21330051920252</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6071,13 +5725,13 @@
         <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6086,27 +5740,27 @@
         <v>65</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920260</v>
+        <v>21330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6114,22 +5768,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920260</v>
+        <v>21330051920261</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6137,39 +5791,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920088</v>
+        <v>21330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6">
         <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920088</v>
+        <v>21330051920255</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6178,27 +5832,27 @@
         <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920251</v>
+        <v>21330051920260</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6206,22 +5860,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920255</v>
+        <v>21330051920262</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6229,45 +5883,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920262</v>
+        <v>21330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10">
         <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920265</v>
+        <v>21330051920088</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
         <v>95</v>
       </c>
-      <c r="D11" t="s">
-        <v>110</v>
-      </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6275,22 +5929,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920267</v>
+        <v>21330051920273</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
         <v>96</v>
       </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6298,22 +5952,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920358</v>
+        <v>21330051420149</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6321,22 +5975,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920268</v>
+        <v>21330051920285</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
         <v>99</v>
       </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6344,116 +5998,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920273</v>
+        <v>21330051920288</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
         <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920361</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051420149</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920285</v>
-      </c>
-      <c r="B18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920288</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -242,60 +242,240 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>ALDUCIN</t>
   </si>
   <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>CRESCENCIO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>HIDALGO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MADRAZO</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PATIÑO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>RUBALCAVA</t>
   </si>
   <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TERCERO</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VALLEJO</t>
   </si>
   <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PETRILLI</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ARCADIO</t>
   </si>
   <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CADENA</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>BENITO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>APONTE</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>NAVA</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>ARAUZ</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>YARELI</t>
+  </si>
+  <si>
     <t>MELANI PAOLA</t>
   </si>
   <si>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>NADIA</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>SUGHEYDI JAZMIN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>EMILIANO</t>
+  </si>
+  <si>
+    <t>LESLY JAREDT</t>
+  </si>
+  <si>
     <t>MARIA TERESA</t>
   </si>
   <si>
@@ -305,277 +485,97 @@
     <t>ANA LILIANA</t>
   </si>
   <si>
+    <t>VENUS</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
+  </si>
+  <si>
+    <t>BIBIAN YANEL</t>
+  </si>
+  <si>
+    <t>ANGELO RENE</t>
+  </si>
+  <si>
+    <t>EVELIN ALEXANDRA</t>
+  </si>
+  <si>
     <t>ANGELINA</t>
   </si>
   <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>DULCE NAOMI</t>
+  </si>
+  <si>
+    <t>ANA PAOLA</t>
+  </si>
+  <si>
+    <t>ALYN</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>MILDRED MARIANA</t>
+  </si>
+  <si>
     <t>MARIANA PAOLA</t>
   </si>
   <si>
+    <t>ANGELICA NAOMI</t>
+  </si>
+  <si>
+    <t>DUILIO</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>JOSE ANGEL</t>
+  </si>
+  <si>
+    <t>BRYAN ABRAHAM</t>
+  </si>
+  <si>
+    <t>ARANTXA</t>
+  </si>
+  <si>
     <t>BRIANDA RENEE</t>
   </si>
   <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>BETHSABE</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>FERNANDO</t>
   </si>
   <si>
+    <t>MAGDA SARAY</t>
+  </si>
+  <si>
+    <t>KARLA GRISELL</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
     <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRAZO</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PETRILLI</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CADENA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>BENITO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APONTE</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARAUZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>YARELI</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>NADIA</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>SUGHEYDI JAZMIN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>EMILIANO</t>
-  </si>
-  <si>
-    <t>LESLY JAREDT</t>
-  </si>
-  <si>
-    <t>VENUS</t>
-  </si>
-  <si>
-    <t>RICARDO ABEL</t>
-  </si>
-  <si>
-    <t>BIBIAN YANEL</t>
-  </si>
-  <si>
-    <t>ANGELO RENE</t>
-  </si>
-  <si>
-    <t>EVELIN ALEXANDRA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>DULCE NAOMI</t>
-  </si>
-  <si>
-    <t>ANA PAOLA</t>
-  </si>
-  <si>
-    <t>ALYN</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MILDRED MARIANA</t>
-  </si>
-  <si>
-    <t>ANGELICA NAOMI</t>
-  </si>
-  <si>
-    <t>DUILIO</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>JOSE ANGEL</t>
-  </si>
-  <si>
-    <t>BRYAN ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARANTXA</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>BETHSABE</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>MAGDA SARAY</t>
-  </si>
-  <si>
-    <t>KARLA GRISELL</t>
-  </si>
-  <si>
-    <t>EZEQUIEL</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1079,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -1088,10 +1088,10 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1115,7 +1115,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1124,10 +1124,10 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1138,7 +1138,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1156,7 +1156,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -1165,10 +1165,10 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1204,7 +1204,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1233,7 +1233,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1242,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1278,10 +1278,10 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1310,7 +1310,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1319,10 +1319,10 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1387,7 +1387,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -1396,10 +1396,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1423,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1464,7 +1464,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1473,10 +1473,10 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1500,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1509,10 +1509,10 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1541,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1550,10 +1550,10 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1586,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1618,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -1627,10 +1627,10 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1663,10 +1663,10 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1704,10 +1704,10 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1731,7 +1731,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1772,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1781,10 +1781,10 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1820,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1831,7 +1831,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>7</v>
@@ -1849,7 +1849,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1858,10 +1858,10 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1897,7 +1897,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1908,7 +1908,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1920,13 +1920,13 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -1935,10 +1935,10 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1962,7 +1962,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1974,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1985,7 +1985,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -2003,7 +2003,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -2012,10 +2012,10 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -2039,7 +2039,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -2080,7 +2080,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -2089,10 +2089,10 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -2128,7 +2128,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2157,7 +2157,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -2166,10 +2166,10 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2193,7 +2193,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2202,10 +2202,10 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2234,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -2243,10 +2243,10 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2311,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -2320,10 +2320,10 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2370,7 +2370,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2388,7 +2388,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2397,10 +2397,10 @@
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2424,7 +2424,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2433,7 +2433,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2465,7 +2465,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -2474,10 +2474,10 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2551,10 +2551,10 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2578,7 +2578,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2587,10 +2587,10 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2619,7 +2619,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2628,10 +2628,10 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2696,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -2705,10 +2705,10 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2782,10 +2782,10 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2821,7 +2821,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2850,7 +2850,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2859,10 +2859,10 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -2927,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2936,10 +2936,10 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2963,7 +2963,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2975,7 +2975,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -3004,7 +3004,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -3013,10 +3013,10 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -3049,7 +3049,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3081,7 +3081,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -3090,10 +3090,10 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3117,7 +3117,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -3158,7 +3158,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -3167,10 +3167,10 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3203,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3235,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3244,10 +3244,10 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -3312,7 +3312,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>7</v>
@@ -3321,10 +3321,10 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3348,7 +3348,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3357,10 +3357,10 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3389,7 +3389,7 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3398,10 +3398,10 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3437,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3448,7 +3448,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -3466,7 +3466,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3475,10 +3475,10 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3502,7 +3502,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3552,10 +3552,10 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3579,7 +3579,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
         <v>9</v>
@@ -3620,7 +3620,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>9</v>
@@ -3629,10 +3629,10 @@
         <v>9</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3668,7 +3668,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3697,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -3706,10 +3706,10 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
         <v>10</v>
@@ -3742,7 +3742,7 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3774,7 +3774,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I39">
         <v>7</v>
@@ -3783,10 +3783,10 @@
         <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>9</v>
@@ -3810,7 +3810,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>8</v>
@@ -3822,7 +3822,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3833,7 +3833,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -3845,13 +3845,13 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -3860,10 +3860,10 @@
         <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>6</v>
@@ -3887,7 +3887,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3896,10 +3896,10 @@
         <v>8</v>
       </c>
       <c r="W40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3910,7 +3910,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>8</v>
@@ -3928,7 +3928,7 @@
         <v>6</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>7</v>
@@ -3937,10 +3937,10 @@
         <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>9</v>
@@ -3964,7 +3964,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>8</v>
@@ -3973,10 +3973,10 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>8</v>
@@ -4005,7 +4005,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>8</v>
@@ -4014,10 +4014,10 @@
         <v>10</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M42">
         <v>7</v>
@@ -4050,10 +4050,10 @@
         <v>10</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4082,7 +4082,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -4091,10 +4091,10 @@
         <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>9</v>
@@ -4118,7 +4118,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -4127,10 +4127,10 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -4159,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>8</v>
@@ -4168,10 +4168,10 @@
         <v>7</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
         <v>9</v>
@@ -4195,7 +4195,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -4207,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="X44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -4218,7 +4218,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>6</v>
@@ -4236,7 +4236,7 @@
         <v>7</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I45">
         <v>9</v>
@@ -4245,10 +4245,10 @@
         <v>9</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M45">
         <v>10</v>
@@ -4272,7 +4272,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U45">
         <v>8</v>
@@ -4313,7 +4313,7 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I46">
         <v>8</v>
@@ -4322,10 +4322,10 @@
         <v>-1</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M46">
         <v>5</v>
@@ -4349,7 +4349,7 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U46">
         <v>9</v>
@@ -4358,7 +4358,7 @@
         <v>9</v>
       </c>
       <c r="W46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X46">
         <v>6</v>
@@ -4432,22 +4432,22 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>77.27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4493,25 +4493,25 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>95.45</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4617,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4642,246 +4642,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920252</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920260</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920261</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920261</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920262</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920088</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920273</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051420149</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920282</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920282</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920285</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920288</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4917,183 +4677,183 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920261</v>
+        <v>21330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920282</v>
+        <v>21330051920252</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920252</v>
+        <v>21330051920253</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920260</v>
+        <v>21330051920254</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920262</v>
+        <v>21330051920255</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920088</v>
+        <v>21330051920256</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920273</v>
+        <v>21330051920257</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051420149</v>
+        <v>21330051920258</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920285</v>
+        <v>21330051920259</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920288</v>
+        <v>21330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920251</v>
+        <v>21330051920261</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
         <v>153</v>
@@ -5104,13 +4864,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920253</v>
+        <v>21330051920262</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
         <v>154</v>
@@ -5121,16 +4881,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920254</v>
+        <v>21330051920263</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5138,16 +4898,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920255</v>
+        <v>21330051920264</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5155,16 +4915,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920256</v>
+        <v>21330051920265</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5172,16 +4932,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920257</v>
+        <v>21330051920266</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5189,16 +4949,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920258</v>
+        <v>21330051920267</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5206,16 +4963,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920259</v>
+        <v>21330051920087</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5223,16 +4980,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920263</v>
+        <v>21330051920088</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5240,13 +4997,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920264</v>
+        <v>21330051920358</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -5257,13 +5014,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920265</v>
+        <v>21330051920268</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5274,13 +5031,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920266</v>
+        <v>21330051920091</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -5291,10 +5048,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920267</v>
+        <v>21330051920270</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5305,13 +5065,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920087</v>
+        <v>21330051920271</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5322,13 +5082,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920358</v>
+        <v>21330051920272</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5339,13 +5099,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920268</v>
+        <v>21330051920273</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>167</v>
@@ -5356,13 +5116,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920091</v>
+        <v>21330051920274</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5373,13 +5133,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920270</v>
+        <v>21330051920361</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5390,13 +5150,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920271</v>
+        <v>21330051920275</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5407,13 +5167,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920272</v>
+        <v>21330051920362</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5424,13 +5184,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920274</v>
+        <v>21330051920276</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5441,13 +5201,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920361</v>
+        <v>21330051920277</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
         <v>173</v>
@@ -5458,13 +5218,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920275</v>
+        <v>21330051920278</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>174</v>
@@ -5475,13 +5235,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920362</v>
+        <v>21330051420149</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>175</v>
@@ -5492,13 +5252,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920276</v>
+        <v>21330051920279</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>176</v>
@@ -5509,13 +5269,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920277</v>
+        <v>21330051920280</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
@@ -5526,13 +5286,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920278</v>
+        <v>21330051920282</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
@@ -5543,13 +5303,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920279</v>
+        <v>21330051920283</v>
       </c>
       <c r="B39" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
         <v>179</v>
@@ -5560,13 +5320,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920280</v>
+        <v>21330051920284</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
         <v>180</v>
@@ -5577,13 +5337,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920283</v>
+        <v>21330051920285</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
         <v>181</v>
@@ -5594,13 +5354,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920284</v>
+        <v>21330051920286</v>
       </c>
       <c r="B42" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -5611,13 +5371,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920286</v>
+        <v>20330051920358</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s">
         <v>183</v>
@@ -5628,13 +5388,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>20330051920358</v>
+        <v>21330051920287</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
         <v>184</v>
@@ -5645,13 +5405,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>21330051920287</v>
+        <v>21330051920288</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
         <v>185</v>
@@ -5667,7 +5427,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5699,16 +5459,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5717,27 +5477,27 @@
         <v>64</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920252</v>
+        <v>21330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5745,68 +5505,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920261</v>
+        <v>21330051920251</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920261</v>
+        <v>21330051920255</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920251</v>
+        <v>21330051920260</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5814,22 +5574,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920255</v>
+        <v>21330051920262</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5837,16 +5597,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920260</v>
+        <v>21330051920267</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5855,21 +5612,21 @@
         <v>64</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920262</v>
+        <v>21330051920088</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -5878,27 +5635,27 @@
         <v>64</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920265</v>
+        <v>21330051920285</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5906,16 +5663,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920088</v>
+        <v>20330051920358</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -5924,99 +5681,7 @@
         <v>64</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920273</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051420149</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920285</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920288</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Morales Vallejo Jorge Luis</t>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1106,16 +1106,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1174,7 +1174,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1183,13 +1183,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1251,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1260,13 +1260,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1328,7 +1328,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1337,13 +1337,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1358,7 +1358,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1405,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1414,13 +1414,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1482,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1491,13 +1491,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1515,7 +1515,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1559,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1568,13 +1568,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1589,10 +1589,10 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1636,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1645,16 +1645,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1663,13 +1663,13 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1713,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1722,16 +1722,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1743,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1790,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1799,13 +1799,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1876,16 +1876,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1944,7 +1944,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1953,13 +1953,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1971,13 +1971,13 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2021,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2030,16 +2030,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -2054,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2098,7 +2098,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2107,13 +2107,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2131,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2175,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2184,13 +2184,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2252,7 +2252,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2261,13 +2261,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2329,7 +2329,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2338,13 +2338,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2406,7 +2406,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2415,16 +2415,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2439,7 +2439,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2483,7 +2483,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2492,16 +2492,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2560,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2569,16 +2569,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2590,7 +2590,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2646,13 +2646,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2714,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2723,13 +2723,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2791,7 +2791,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2800,13 +2800,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2868,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2877,13 +2877,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2954,13 +2954,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3022,7 +3022,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3031,16 +3031,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -3055,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3108,16 +3108,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -3129,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3176,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3185,13 +3185,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3206,10 +3206,10 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3238,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3262,19 +3262,19 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3283,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3339,16 +3339,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3357,10 +3357,10 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3407,7 +3407,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3416,13 +3416,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>7</v>
@@ -3437,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3493,16 +3493,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3561,7 +3561,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3570,16 +3570,16 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>9</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3647,13 +3647,13 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3668,7 +3668,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3715,7 +3715,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3724,13 +3724,13 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3742,10 +3742,10 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>9</v>
@@ -3792,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3801,13 +3801,13 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>7</v>
@@ -3819,10 +3819,10 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3869,7 +3869,7 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3878,13 +3878,13 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3896,13 +3896,13 @@
         <v>8</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3946,7 +3946,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3955,13 +3955,13 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -3973,13 +3973,13 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -4023,7 +4023,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -4032,13 +4032,13 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -4050,10 +4050,10 @@
         <v>10</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4100,7 +4100,7 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>-1</v>
@@ -4109,16 +4109,16 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -4133,7 +4133,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4177,7 +4177,7 @@
         <v>9</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>-1</v>
@@ -4186,16 +4186,16 @@
         <v>-1</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -4254,7 +4254,7 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
         <v>-1</v>
@@ -4263,16 +4263,16 @@
         <v>-1</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U45">
         <v>8</v>
@@ -4284,7 +4284,7 @@
         <v>10</v>
       </c>
       <c r="X45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y45">
         <v>9</v>
@@ -4331,7 +4331,7 @@
         <v>5</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>-1</v>
@@ -4340,13 +4340,13 @@
         <v>-1</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T46">
         <v>6</v>
@@ -4364,7 +4364,7 @@
         <v>6</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4429,19 +4429,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>77.27</v>
+        <v>88.64</v>
       </c>
       <c r="G2">
-        <v>22.73</v>
+        <v>11.36</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4461,19 +4461,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>88.64</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="G3">
-        <v>11.36</v>
+        <v>6.82</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4493,19 +4493,19 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>90.91</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="G4">
-        <v>9.09</v>
+        <v>6.82</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5427,7 +5427,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5459,16 +5459,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920261</v>
+        <v>21330051920282</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5482,205 +5482,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920261</v>
+        <v>21330051920285</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920251</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920255</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920260</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920262</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920267</v>
-      </c>
-      <c r="B8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920088</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920285</v>
-      </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920358</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20212.xlsx
+++ b/grupos/2ALCM - Estadisticos 20212.xlsx
@@ -1100,10 +1100,10 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -1177,10 +1177,10 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>5</v>
@@ -1254,10 +1254,10 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1331,10 +1331,10 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1408,10 +1408,10 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1485,10 +1485,10 @@
         <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1503,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1562,10 +1562,10 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1639,10 +1639,10 @@
         <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1657,7 +1657,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1716,10 +1716,10 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1734,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1793,10 +1793,10 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1870,10 +1870,10 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1932,7 +1932,7 @@
         <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -1947,10 +1947,10 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -2024,10 +2024,10 @@
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2042,7 +2042,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2101,10 +2101,10 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -2178,10 +2178,10 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2255,10 +2255,10 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2332,10 +2332,10 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2409,10 +2409,10 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2427,7 +2427,7 @@
         <v>6</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2486,10 +2486,10 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2504,7 +2504,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2563,10 +2563,10 @@
         <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2581,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2640,10 +2640,10 @@
         <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2717,10 +2717,10 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>10</v>
@@ -2794,10 +2794,10 @@
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2812,7 +2812,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2871,10 +2871,10 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2948,10 +2948,10 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -3025,10 +3025,10 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -3043,7 +3043,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -3102,10 +3102,10 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3179,10 +3179,10 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3256,10 +3256,10 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>9</v>
@@ -3333,10 +3333,10 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3410,10 +3410,10 @@
         <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>9</v>
@@ -3487,10 +3487,10 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3505,7 +3505,7 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3564,10 +3564,10 @@
         <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3641,10 +3641,10 @@
         <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>10</v>
@@ -3718,10 +3718,10 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>9</v>
@@ -3795,10 +3795,10 @@
         <v>6</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3872,10 +3872,10 @@
         <v>5</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>10</v>
@@ -3949,10 +3949,10 @@
         <v>5</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>9</v>
@@ -3967,7 +3967,7 @@
         <v>5</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -4026,10 +4026,10 @@
         <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>9</v>
@@ -4103,10 +4103,10 @@
         <v>6</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
         <v>10</v>
@@ -4121,7 +4121,7 @@
         <v>7</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -4180,10 +4180,10 @@
         <v>7</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>6</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V44">
         <v>8</v>
@@ -4257,10 +4257,10 @@
         <v>10</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
         <v>10</v>
@@ -4275,7 +4275,7 @@
         <v>8</v>
       </c>
       <c r="U45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V45">
         <v>10</v>
@@ -4319,7 +4319,7 @@
         <v>8</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K46">
         <v>8</v>
@@ -4334,10 +4334,10 @@
         <v>6</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q46">
         <v>10</v>
@@ -4352,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="U46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V46">
         <v>9</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
